--- a/output/central_unit_requests/Education - SR26 sustainability reporting request.xlsx
+++ b/output/central_unit_requests/Education - SR26 sustainability reporting request.xlsx
@@ -627,7 +627,7 @@
     <col width="38" customWidth="1" min="5" max="5"/>
     <col width="50" customWidth="1" min="6" max="6"/>
     <col width="34" customWidth="1" min="7" max="7"/>
-    <col width="11" customWidth="1" min="8" max="8"/>
+    <col width="18" customWidth="1" min="8" max="8"/>
     <col hidden="1" width="16" customWidth="1" min="9" max="9"/>
     <col hidden="1" width="50" customWidth="1" min="10" max="10"/>
     <col hidden="1" width="24" customWidth="1" min="11" max="11"/>
@@ -648,7 +648,7 @@
       </c>
       <c r="B1" s="2" t="inlineStr">
         <is>
-          <t>End-2026 target status assessment and reporting (v0.12)</t>
+          <t>End-2026 target status assessment and reporting (v0.13)</t>
         </is>
       </c>
     </row>
@@ -756,7 +756,7 @@
       </c>
       <c r="H13" s="12" t="inlineStr">
         <is>
-          <t>End-2025 reporting (click the ref to see your full SR25 response)</t>
+          <t>SR25 response</t>
         </is>
       </c>
       <c r="L13" s="13" t="inlineStr">
@@ -1065,9 +1065,8 @@
     <row r="19"/>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="1"/>
-  <mergeCells count="10">
+  <mergeCells count="9">
     <mergeCell ref="M7:N7"/>
-    <mergeCell ref="H13:K13"/>
     <mergeCell ref="B4:C8"/>
     <mergeCell ref="M6:N6"/>
     <mergeCell ref="L13:R13"/>

--- a/output/central_unit_requests/Education - SR26 sustainability reporting request.xlsx
+++ b/output/central_unit_requests/Education - SR26 sustainability reporting request.xlsx
@@ -20,7 +20,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="20">
+  <fonts count="18">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -78,18 +78,6 @@
       <sz val="11"/>
     </font>
     <font>
-      <name val="Aptos"/>
-      <b val="1"/>
-    </font>
-    <font>
-      <name val="Aptos"/>
-    </font>
-    <font>
-      <name val="Aptos"/>
-      <i val="1"/>
-      <sz val="9"/>
-    </font>
-    <font>
       <name val="Aptos Narrow"/>
       <b val="1"/>
       <sz val="22"/>
@@ -125,8 +113,12 @@
       <sz val="11"/>
       <u val="single"/>
     </font>
+    <font>
+      <name val="Aptos"/>
+      <b val="1"/>
+    </font>
   </fonts>
-  <fills count="7">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -146,11 +138,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00C1E4F5"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00D9D9D9"/>
       </patternFill>
     </fill>
     <fill>
@@ -191,38 +178,31 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="9" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -234,13 +214,14 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
       <protection locked="0" hidden="0"/>
     </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -617,7 +598,7 @@
     <outlinePr summaryBelow="1" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R19"/>
+  <dimension ref="A1:Q19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -631,13 +612,12 @@
     <col hidden="1" width="16" customWidth="1" min="9" max="9"/>
     <col hidden="1" width="50" customWidth="1" min="10" max="10"/>
     <col hidden="1" width="24" customWidth="1" min="11" max="11"/>
-    <col width="22" customWidth="1" min="12" max="12"/>
+    <col width="48" customWidth="1" min="12" max="12"/>
     <col width="48" customWidth="1" min="13" max="13"/>
-    <col width="48" customWidth="1" min="14" max="14"/>
+    <col width="30" customWidth="1" min="14" max="14"/>
     <col width="30" customWidth="1" min="15" max="15"/>
-    <col width="30" customWidth="1" min="16" max="16"/>
-    <col width="20" customWidth="1" min="17" max="17"/>
-    <col width="24" customWidth="1" min="18" max="18"/>
+    <col width="20" customWidth="1" min="16" max="16"/>
+    <col width="24" customWidth="1" min="17" max="17"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -648,439 +628,356 @@
       </c>
       <c r="B1" s="2" t="inlineStr">
         <is>
-          <t>End-2026 target status assessment and reporting (v0.13)</t>
+          <t>SR26 sustainability reporting (v0.14)</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>End-2026 target status confirmation and reporting</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="L3" s="4" t="inlineStr">
-        <is>
-          <t>Target status assessment and definitions</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="32" customHeight="1">
-      <c r="B4" s="5" t="inlineStr">
+          <t>SR26 sustainability reporting request</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="B4" s="4" t="inlineStr">
         <is>
           <t>How to use this spreadsheet:</t>
         </is>
       </c>
-      <c r="D4" s="6" t="inlineStr">
-        <is>
-          <t>• Confirm target status for each row below (Column L). Refer to target status definitions to the right for guidance.
-• Provide commentary on progress towards each target (Column M or N)
-• Provide supporting documentation if required (Column O), including links to images
-• Note the source of your information and any limitations (Column P), then confirm the information is accurate (Columns Q–R)
+      <c r="D4" s="5" t="inlineStr">
+        <is>
+          <t>• For each row below, describe progress towards the target (Column L) and/or respond to the 2026 reporting request (Column M)
+• Provide supporting information if required (Column N), including links to documents or images
+• Note the source of your information and any limitations (Column O), then confirm the information is accurate (Columns P–Q)
 • Where a related end-2025 target existed, click the ref in Column H to see your full SR25 response (Tab 3)
 • Use Tab 2 of this spreadsheet to highlight key sustainability stories (optional)
-• 2026 is a transition year: Sustainability 2030 launched ~20 October 2026, so report on activity across all of 2026 and any early actions since launch.
+• 2026 is a transition year: Sustainability 2030 launched ~20 October 2026, so report on activity across all of 2026 and any early actions since launch. No target status rating is requested this year.
 • Due: Tuesday 15 December 2026. Questions: CDSS – questions and clarifications are recorded centrally (contact email TBC); optional 1:1 meetings available on request</t>
         </is>
       </c>
-      <c r="L4" s="7" t="inlineStr">
-        <is>
-          <t>Met or exceeded</t>
-        </is>
-      </c>
-      <c r="M4" s="8" t="inlineStr">
-        <is>
-          <t>The data and information provided demonstrates that the Faculty/Portfolio has met or exceeded the target</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="32" customHeight="1">
-      <c r="L5" s="7" t="inlineStr">
-        <is>
-          <t>Partially met</t>
-        </is>
-      </c>
-      <c r="M5" s="8" t="inlineStr">
-        <is>
-          <t>The data and information provided indicates that the target has not been met, but there has been a significant improvement and performance is trending towards the target</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="32" customHeight="1">
-      <c r="L6" s="7" t="inlineStr">
-        <is>
-          <t>Not met</t>
-        </is>
-      </c>
-      <c r="M6" s="8" t="inlineStr">
-        <is>
-          <t>Some action has been taken to address the target, but the data and information provided demonstrates that this has been insufficient to meet the target</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="32" customHeight="1">
-      <c r="L7" s="7" t="inlineStr">
-        <is>
-          <t>Not yet started</t>
-        </is>
-      </c>
-      <c r="M7" s="8" t="inlineStr">
-        <is>
-          <t>No action has been taken.</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="60" customHeight="1">
-      <c r="L8" s="9" t="n"/>
-    </row>
-    <row r="9">
-      <c r="L9" s="10" t="inlineStr">
-        <is>
-          <t>Note: target status definitions are under review for 2027 reporting. 2026 ratings are for internal management reporting only.</t>
-        </is>
-      </c>
-    </row>
+    </row>
+    <row r="5"/>
+    <row r="6"/>
+    <row r="7"/>
+    <row r="8" ht="60" customHeight="1"/>
     <row r="11">
-      <c r="B11" s="11" t="inlineStr">
+      <c r="B11" s="6" t="inlineStr">
         <is>
           <t>Education – Chancellery Education</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="C13" s="12" t="inlineStr">
+      <c r="C13" s="7" t="inlineStr">
         <is>
           <t>Sustainability 2030 target and indicator</t>
         </is>
       </c>
-      <c r="H13" s="12" t="inlineStr">
+      <c r="H13" s="7" t="inlineStr">
         <is>
           <t>SR25 response</t>
         </is>
       </c>
-      <c r="L13" s="13" t="inlineStr">
+      <c r="L13" s="8" t="inlineStr">
         <is>
           <t>End-2026 reporting (PLEASE COMPLETE THIS SECTION)</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="B14" s="14" t="inlineStr">
+      <c r="B14" s="9" t="inlineStr">
         <is>
           <t>Ref</t>
         </is>
       </c>
-      <c r="C14" s="14" t="inlineStr">
+      <c r="C14" s="9" t="inlineStr">
         <is>
           <t>Priority area</t>
         </is>
       </c>
-      <c r="D14" s="14" t="inlineStr">
+      <c r="D14" s="9" t="inlineStr">
         <is>
           <t>Sustainability 2030 target</t>
         </is>
       </c>
-      <c r="E14" s="14" t="inlineStr">
+      <c r="E14" s="9" t="inlineStr">
         <is>
           <t>Indicator</t>
         </is>
       </c>
-      <c r="F14" s="14" t="inlineStr">
+      <c r="F14" s="9" t="inlineStr">
         <is>
           <t>2026 Reporting request</t>
         </is>
       </c>
-      <c r="G14" s="14" t="inlineStr">
+      <c r="G14" s="9" t="inlineStr">
         <is>
           <t>How SST will use this data</t>
         </is>
       </c>
-      <c r="H14" s="14" t="inlineStr">
+      <c r="H14" s="9" t="inlineStr">
         <is>
           <t>Related SR25 ref</t>
         </is>
       </c>
-      <c r="I14" s="14" t="inlineStr">
+      <c r="I14" s="9" t="inlineStr">
         <is>
           <t>End-2025 confirmed status</t>
         </is>
       </c>
-      <c r="J14" s="14" t="inlineStr">
+      <c r="J14" s="9" t="inlineStr">
         <is>
           <t>End-2025 reporting response</t>
         </is>
       </c>
-      <c r="K14" s="14" t="inlineStr">
+      <c r="K14" s="9" t="inlineStr">
         <is>
           <t>Links and supporting information</t>
         </is>
       </c>
-      <c r="L14" s="15" t="inlineStr">
-        <is>
-          <t>Confirm end-2026 target status</t>
-        </is>
-      </c>
-      <c r="M14" s="15" t="inlineStr">
+      <c r="L14" s="10" t="inlineStr">
         <is>
           <t>OPTION 1:  Target-level reporting (Column D)</t>
         </is>
       </c>
-      <c r="N14" s="15" t="inlineStr">
+      <c r="M14" s="10" t="inlineStr">
         <is>
           <t>OPTION 2:  Indicator level reporting (Column E/F)</t>
         </is>
       </c>
-      <c r="O14" s="15" t="inlineStr">
+      <c r="N14" s="10" t="inlineStr">
         <is>
           <t>Supporting information/comments</t>
         </is>
       </c>
-      <c r="P14" s="15" t="inlineStr">
+      <c r="O14" s="10" t="inlineStr">
         <is>
           <t>Data source and limitations</t>
         </is>
       </c>
-      <c r="Q14" s="15" t="inlineStr">
+      <c r="P14" s="10" t="inlineStr">
         <is>
           <t>Data owner confirms information is accurate</t>
         </is>
       </c>
-      <c r="R14" s="15" t="inlineStr">
+      <c r="Q14" s="10" t="inlineStr">
         <is>
           <t>Confirmed by (name, role, date)</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="B15" s="16" t="inlineStr"/>
-      <c r="C15" s="16" t="inlineStr"/>
-      <c r="D15" s="16" t="inlineStr"/>
-      <c r="E15" s="16" t="inlineStr"/>
-      <c r="F15" s="16" t="inlineStr"/>
-      <c r="G15" s="16" t="inlineStr"/>
-      <c r="H15" s="16" t="inlineStr"/>
-      <c r="I15" s="16" t="inlineStr"/>
-      <c r="J15" s="16" t="inlineStr"/>
-      <c r="K15" s="16" t="inlineStr"/>
-      <c r="L15" s="16" t="inlineStr">
-        <is>
-          <t>(Met or exceeded; partially met; not met; not yet started)</t>
-        </is>
-      </c>
-      <c r="M15" s="16" t="inlineStr">
-        <is>
-          <t>Provide further evidence of target status assessment in the form of:
-A general update on activities in relation to the overarching target (Column D)</t>
-        </is>
-      </c>
-      <c r="N15" s="16" t="inlineStr">
-        <is>
-          <t>Provide further evidence of target status assessment in the form of:
-Data and commentary in direct response to the reporting request (Column F)</t>
-        </is>
-      </c>
-      <c r="O15" s="16" t="inlineStr">
-        <is>
-          <t>Provide any additional information to support the target status assessment (e.g. links, images, rationale for selection of target status)</t>
-        </is>
-      </c>
-      <c r="P15" s="16" t="inlineStr">
+      <c r="B15" s="11" t="inlineStr"/>
+      <c r="C15" s="11" t="inlineStr"/>
+      <c r="D15" s="11" t="inlineStr"/>
+      <c r="E15" s="11" t="inlineStr"/>
+      <c r="F15" s="11" t="inlineStr"/>
+      <c r="G15" s="11" t="inlineStr"/>
+      <c r="H15" s="11" t="inlineStr"/>
+      <c r="I15" s="11" t="inlineStr"/>
+      <c r="J15" s="11" t="inlineStr"/>
+      <c r="K15" s="11" t="inlineStr"/>
+      <c r="L15" s="11" t="inlineStr">
+        <is>
+          <t>A general update on activities in relation to the overarching target (Column D)</t>
+        </is>
+      </c>
+      <c r="M15" s="11" t="inlineStr">
+        <is>
+          <t>Data and commentary in direct response to the reporting request (Column F)</t>
+        </is>
+      </c>
+      <c r="N15" s="11" t="inlineStr">
+        <is>
+          <t>Any additional information (e.g. links, images, documents)</t>
+        </is>
+      </c>
+      <c r="O15" s="11" t="inlineStr">
         <is>
           <t>Where did this information come from (system, report, survey, person)? Note any gaps or limitations.</t>
         </is>
       </c>
-      <c r="Q15" s="16" t="inlineStr">
+      <c r="P15" s="11" t="inlineStr">
         <is>
           <t>Select 'Yes' to confirm the information provided is accurate and can be used for reporting</t>
         </is>
       </c>
-      <c r="R15" s="16" t="inlineStr">
+      <c r="Q15" s="11" t="inlineStr">
         <is>
           <t>Name, role and date of the person confirming</t>
         </is>
       </c>
     </row>
     <row r="16" ht="150" customHeight="1">
-      <c r="B16" s="17" t="inlineStr">
+      <c r="B16" s="12" t="inlineStr">
         <is>
           <t>EE1(a)</t>
         </is>
       </c>
-      <c r="C16" s="18" t="inlineStr">
+      <c r="C16" s="13" t="inlineStr">
         <is>
           <t>Exceptional education</t>
         </is>
       </c>
-      <c r="D16" s="18" t="inlineStr">
+      <c r="D16" s="13" t="inlineStr">
         <is>
           <t>Provide our students with learning experiences that help them build the knowledge, skills and relationships to lead change for sustainable societies.</t>
         </is>
       </c>
-      <c r="E16" s="18" t="inlineStr">
+      <c r="E16" s="13" t="inlineStr">
         <is>
           <t>Evidence of innovative approaches to sustainability teaching and learning</t>
         </is>
       </c>
-      <c r="F16" s="19" t="inlineStr">
-        <is>
-          <t>In end-2025 reporting your area reported on the related SP2030 target 4a(ii) and rated it 'Not yet started' (click the ref in Column H to see it in full in Tab 3). Please build on this rather than repeating it, focusing on what is new in 2026.
+      <c r="F16" s="14" t="inlineStr">
+        <is>
+          <t>In end-2025 reporting your area reported on the related SP2030 target 4a(ii) (click the ref in Column H to see it in full in Tab 3). Please build on this rather than repeating it, focusing on what is new in 2026.
 Please describe any innovative approaches used within your Faculty/Portfolio to embed sustainability in teaching and learning. This could include examples of subjects, curriculum design, pedagogies, assessment approaches or learning resources. Please provide links or supporting evidence where available.</t>
         </is>
       </c>
-      <c r="G16" s="19" t="inlineStr">
+      <c r="G16" s="14" t="inlineStr">
         <is>
           <t>We will collate examples of sustainability teaching and learning, including experiential and co-curricular learning, across faculties to inform the Exceptional education section of the 2026 Sustainability Report. Strong examples may be followed up for the report.</t>
         </is>
       </c>
-      <c r="H16" s="20" t="inlineStr">
+      <c r="H16" s="15" t="inlineStr">
         <is>
           <t>4a(ii)
 → view SR25 response</t>
         </is>
       </c>
-      <c r="I16" s="19" t="inlineStr">
+      <c r="I16" s="14" t="inlineStr">
         <is>
           <t>Not yet started</t>
         </is>
       </c>
-      <c r="J16" s="19" t="inlineStr">
+      <c r="J16" s="14" t="inlineStr">
         <is>
           <t>The Joining Melbourne Module on sustainability is available to all commencing undergraduate students, and several Discovery subjects (completed by all commencing undergraduate students) embed sustainability themes. Work on embedded sustainability within the curriculum is underway at the faculty-level despite the unfunded nature of the sustainability touchstone work planned within ASE.</t>
         </is>
       </c>
-      <c r="K16" s="19" t="inlineStr">
+      <c r="K16" s="14" t="inlineStr">
         <is>
           <t>As per mid-2025: this is unfunded (including new curriculum management system). Faculties are pursuing this but central efforts are on hold.</t>
         </is>
       </c>
-      <c r="L16" s="21" t="n"/>
-      <c r="M16" s="21" t="n"/>
-      <c r="N16" s="21" t="n"/>
-      <c r="O16" s="21" t="n"/>
-      <c r="P16" s="21" t="n"/>
-      <c r="Q16" s="21" t="n"/>
-      <c r="R16" s="21" t="n"/>
+      <c r="L16" s="16" t="n"/>
+      <c r="M16" s="16" t="n"/>
+      <c r="N16" s="16" t="n"/>
+      <c r="O16" s="16" t="n"/>
+      <c r="P16" s="16" t="n"/>
+      <c r="Q16" s="16" t="n"/>
     </row>
     <row r="17" ht="150" customHeight="1">
-      <c r="B17" s="17" t="inlineStr">
+      <c r="B17" s="12" t="inlineStr">
         <is>
           <t>EE1(b)</t>
         </is>
       </c>
-      <c r="C17" s="18" t="inlineStr">
+      <c r="C17" s="13" t="inlineStr">
         <is>
           <t>Exceptional education</t>
         </is>
       </c>
-      <c r="D17" s="18" t="inlineStr">
+      <c r="D17" s="13" t="inlineStr">
         <is>
           <t>Provide our students with learning experiences that help them build the knowledge, skills and relationships to lead change for sustainable societies.</t>
         </is>
       </c>
-      <c r="E17" s="18" t="inlineStr">
+      <c r="E17" s="13" t="inlineStr">
         <is>
           <t>Pilots of possible approaches for understanding and developing students’ sustainability self-efficacy</t>
         </is>
       </c>
-      <c r="F17" s="19" t="inlineStr">
+      <c r="F17" s="14" t="inlineStr">
         <is>
           <t>Please describe any pilots or trials undertaken within your Faculty/Portfolio to understand or strengthen students’ sustainability self-efficacy. This could include the approach used, participating cohorts, what was assessed or learned, and any planned next steps.</t>
         </is>
       </c>
-      <c r="G17" s="19" t="inlineStr">
+      <c r="G17" s="14" t="inlineStr">
         <is>
           <t>This is a new indicator. We will use responses to establish a baseline of how (and whether) faculties are understanding student sustainability self-efficacy, and report on early pilots in the 2026 Sustainability Report. A nil response is useful to us.</t>
         </is>
       </c>
-      <c r="H17" s="19" t="inlineStr">
+      <c r="H17" s="14" t="inlineStr">
         <is>
           <t>N/A – new indicator</t>
         </is>
       </c>
-      <c r="I17" s="19" t="inlineStr"/>
-      <c r="J17" s="19" t="inlineStr"/>
-      <c r="K17" s="19" t="inlineStr"/>
-      <c r="L17" s="21" t="n"/>
-      <c r="M17" s="21" t="n"/>
-      <c r="N17" s="21" t="n"/>
-      <c r="O17" s="21" t="n"/>
-      <c r="P17" s="21" t="n"/>
-      <c r="Q17" s="21" t="n"/>
-      <c r="R17" s="21" t="n"/>
+      <c r="I17" s="14" t="inlineStr"/>
+      <c r="J17" s="14" t="inlineStr"/>
+      <c r="K17" s="14" t="inlineStr"/>
+      <c r="L17" s="16" t="n"/>
+      <c r="M17" s="16" t="n"/>
+      <c r="N17" s="16" t="n"/>
+      <c r="O17" s="16" t="n"/>
+      <c r="P17" s="16" t="n"/>
+      <c r="Q17" s="16" t="n"/>
     </row>
     <row r="18" ht="150" customHeight="1">
-      <c r="B18" s="17" t="inlineStr">
+      <c r="B18" s="12" t="inlineStr">
         <is>
           <t>EN1(c)</t>
         </is>
       </c>
-      <c r="C18" s="18" t="inlineStr">
+      <c r="C18" s="13" t="inlineStr">
         <is>
           <t>Enablers</t>
         </is>
       </c>
-      <c r="D18" s="18" t="inlineStr">
+      <c r="D18" s="13" t="inlineStr">
         <is>
           <t>Enablers</t>
         </is>
       </c>
-      <c r="E18" s="18" t="inlineStr">
+      <c r="E18" s="13" t="inlineStr">
         <is>
           <t>Coordinated internal engagement and external partnerships contributing to delivery of sustainability outcomes across priority areas.</t>
         </is>
       </c>
-      <c r="F18" s="19" t="inlineStr">
+      <c r="F18" s="14" t="inlineStr">
         <is>
           <t>We did not receive an end-2025 response for the related SP2030 target 3a(ii), so please include any relevant activity from across 2026.
 Please provide examples of internal engagement or external partnerships involving your Faculty/Portfolio that contributed to Sustainability 2030 outcomes, could include the priority area addressed, participating groups/partners, nature of the collaboration and key outcomes.</t>
         </is>
       </c>
-      <c r="G18" s="19" t="inlineStr">
+      <c r="G18" s="14" t="inlineStr">
         <is>
           <t>We will report on internal engagement and partnerships contributing to Sustainability 2030 outcomes, and update our record of sustainability-focused communities of practice and contacts across the University.</t>
         </is>
       </c>
-      <c r="H18" s="20" t="inlineStr">
+      <c r="H18" s="15" t="inlineStr">
         <is>
           <t>3a(ii)
 → view SR25 response</t>
         </is>
       </c>
-      <c r="I18" s="19" t="inlineStr"/>
-      <c r="J18" s="19" t="inlineStr"/>
-      <c r="K18" s="19" t="inlineStr">
+      <c r="I18" s="14" t="inlineStr"/>
+      <c r="J18" s="14" t="inlineStr"/>
+      <c r="K18" s="14" t="inlineStr">
         <is>
           <t>As per mid-2025: this is not relevant to Ed portfolio. Suggest removing.</t>
         </is>
       </c>
-      <c r="L18" s="21" t="n"/>
-      <c r="M18" s="21" t="n"/>
-      <c r="N18" s="21" t="n"/>
-      <c r="O18" s="21" t="n"/>
-      <c r="P18" s="21" t="n"/>
-      <c r="Q18" s="21" t="n"/>
-      <c r="R18" s="21" t="n"/>
+      <c r="L18" s="16" t="n"/>
+      <c r="M18" s="16" t="n"/>
+      <c r="N18" s="16" t="n"/>
+      <c r="O18" s="16" t="n"/>
+      <c r="P18" s="16" t="n"/>
+      <c r="Q18" s="16" t="n"/>
     </row>
     <row r="19"/>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="1"/>
-  <mergeCells count="9">
-    <mergeCell ref="M7:N7"/>
+  <mergeCells count="4">
+    <mergeCell ref="C13:G13"/>
+    <mergeCell ref="L13:Q13"/>
+    <mergeCell ref="D4:G8"/>
     <mergeCell ref="B4:C8"/>
-    <mergeCell ref="M6:N6"/>
-    <mergeCell ref="L13:R13"/>
-    <mergeCell ref="M5:N5"/>
-    <mergeCell ref="D4:G8"/>
-    <mergeCell ref="C13:G13"/>
-    <mergeCell ref="L3:N3"/>
-    <mergeCell ref="M4:N4"/>
   </mergeCells>
-  <dataValidations count="2">
-    <dataValidation sqref="L16:L18" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid entry" error="Please select from the dropdown" type="list">
-      <formula1>=Lists!$B$3:$B$7</formula1>
-    </dataValidation>
-    <dataValidation sqref="Q16:Q18" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid entry" error="Please select from the dropdown" type="list">
+  <dataValidations count="1">
+    <dataValidation sqref="P16:P18" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid entry" error="Please select from the dropdown" type="list">
       <formula1>=Lists!$C$2:$C$4</formula1>
     </dataValidation>
   </dataValidations>
@@ -1121,7 +1018,7 @@
       </c>
       <c r="B1" s="2" t="inlineStr">
         <is>
-          <t>End-2026 target status assessment and reporting</t>
+          <t>SR26 sustainability reporting</t>
         </is>
       </c>
     </row>
@@ -1133,12 +1030,12 @@
       </c>
     </row>
     <row r="5">
-      <c r="B5" s="7" t="inlineStr">
+      <c r="B5" s="17" t="inlineStr">
         <is>
           <t>How to use this spreadsheet</t>
         </is>
       </c>
-      <c r="C5" s="22" t="inlineStr">
+      <c r="C5" s="18" t="inlineStr">
         <is>
           <t>Please share up to 3 stories from 2026 which highlight your faculty's/portfolio's sustainability progress and/or impact. These stories can directly relate to Sustainability 2030 targets and indicators, or sustainability more generally. Due: Tuesday 15 December 2026 (early submission helps us develop case studies).</t>
         </is>
@@ -1146,77 +1043,77 @@
     </row>
     <row r="6"/>
     <row r="8">
-      <c r="B8" s="23" t="inlineStr">
+      <c r="B8" s="19" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="C8" s="23" t="inlineStr">
+      <c r="C8" s="19" t="inlineStr">
         <is>
           <t>Description</t>
         </is>
       </c>
-      <c r="D8" s="23" t="inlineStr">
+      <c r="D8" s="19" t="inlineStr">
         <is>
           <t>Related Sustainability 2030 targets (optional)</t>
         </is>
       </c>
-      <c r="E8" s="23" t="inlineStr">
+      <c r="E8" s="19" t="inlineStr">
         <is>
           <t>Images and other media</t>
         </is>
       </c>
-      <c r="F8" s="23" t="inlineStr">
+      <c r="F8" s="19" t="inlineStr">
         <is>
           <t>Links and supporting documentation</t>
         </is>
       </c>
     </row>
     <row r="9" ht="90" customHeight="1">
-      <c r="B9" s="24" t="inlineStr"/>
-      <c r="C9" s="24" t="inlineStr">
+      <c r="B9" s="20" t="inlineStr"/>
+      <c r="C9" s="20" t="inlineStr">
         <is>
           <t>• Please include a brief description of a project or activity that has made a significant contribution to sustainability at the University (up to 250 words)
 • Summarise the benefits. Benefits may relate to operational outcomes, environmental/social outcomes, and sector benefits.</t>
         </is>
       </c>
-      <c r="D9" s="24" t="inlineStr"/>
-      <c r="E9" s="24" t="inlineStr">
+      <c r="D9" s="20" t="inlineStr"/>
+      <c r="E9" s="20" t="inlineStr">
         <is>
           <t>(link to OneDrive/SharePoint files or published online content preferred)</t>
         </is>
       </c>
-      <c r="F9" s="24" t="inlineStr"/>
+      <c r="F9" s="20" t="inlineStr"/>
     </row>
     <row r="10" ht="120" customHeight="1">
       <c r="A10" t="n">
         <v>1</v>
       </c>
-      <c r="B10" s="21" t="n"/>
-      <c r="C10" s="21" t="n"/>
-      <c r="D10" s="21" t="n"/>
-      <c r="E10" s="21" t="n"/>
-      <c r="F10" s="21" t="n"/>
+      <c r="B10" s="16" t="n"/>
+      <c r="C10" s="16" t="n"/>
+      <c r="D10" s="16" t="n"/>
+      <c r="E10" s="16" t="n"/>
+      <c r="F10" s="16" t="n"/>
     </row>
     <row r="11" ht="120" customHeight="1">
       <c r="A11" t="n">
         <v>2</v>
       </c>
-      <c r="B11" s="21" t="n"/>
-      <c r="C11" s="21" t="n"/>
-      <c r="D11" s="21" t="n"/>
-      <c r="E11" s="21" t="n"/>
-      <c r="F11" s="21" t="n"/>
+      <c r="B11" s="16" t="n"/>
+      <c r="C11" s="16" t="n"/>
+      <c r="D11" s="16" t="n"/>
+      <c r="E11" s="16" t="n"/>
+      <c r="F11" s="16" t="n"/>
     </row>
     <row r="12" ht="120" customHeight="1">
       <c r="A12" t="n">
         <v>3</v>
       </c>
-      <c r="B12" s="21" t="n"/>
-      <c r="C12" s="21" t="n"/>
-      <c r="D12" s="21" t="n"/>
-      <c r="E12" s="21" t="n"/>
-      <c r="F12" s="21" t="n"/>
+      <c r="B12" s="16" t="n"/>
+      <c r="C12" s="16" t="n"/>
+      <c r="D12" s="16" t="n"/>
+      <c r="E12" s="16" t="n"/>
+      <c r="F12" s="16" t="n"/>
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="1"/>
@@ -1267,233 +1164,233 @@
       </c>
     </row>
     <row r="3" ht="32" customHeight="1">
-      <c r="B3" s="22" t="inlineStr">
+      <c r="B3" s="18" t="inlineStr">
         <is>
           <t>Your responses to the end-2025 reporting request, against the former Sustainability Plan 2030 (SP2030) targets. For reference only – please do not edit. Use the 'Back to request' links to return to the reporting template.</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="B4" s="25" t="inlineStr">
+      <c r="B4" s="21" t="inlineStr">
         <is>
           <t>← Back to request</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="B5" s="26" t="inlineStr">
+      <c r="B5" s="22" t="inlineStr">
         <is>
           <t>Chancellery Education</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="B6" s="14" t="inlineStr">
+      <c r="B6" s="9" t="inlineStr">
         <is>
           <t>SR25 ref</t>
         </is>
       </c>
-      <c r="C6" s="14" t="inlineStr">
+      <c r="C6" s="9" t="inlineStr">
         <is>
           <t>SP2030 target</t>
         </is>
       </c>
-      <c r="D6" s="14" t="inlineStr">
+      <c r="D6" s="9" t="inlineStr">
         <is>
           <t>2025 reporting request</t>
         </is>
       </c>
-      <c r="E6" s="14" t="inlineStr">
+      <c r="E6" s="9" t="inlineStr">
         <is>
           <t>Confirmed end-2025 status</t>
         </is>
       </c>
-      <c r="F6" s="14" t="inlineStr">
+      <c r="F6" s="9" t="inlineStr">
         <is>
           <t>OPTION 1: Target-level reporting</t>
         </is>
       </c>
-      <c r="G6" s="14" t="inlineStr">
+      <c r="G6" s="9" t="inlineStr">
         <is>
           <t>OPTION 2: Indicator-level reporting</t>
         </is>
       </c>
-      <c r="H6" s="14" t="inlineStr">
+      <c r="H6" s="9" t="inlineStr">
         <is>
           <t>Supporting information/comments</t>
         </is>
       </c>
-      <c r="I6" s="14" t="inlineStr">
+      <c r="I6" s="9" t="inlineStr">
         <is>
           <t>Related SR26 indicator(s)</t>
         </is>
       </c>
     </row>
     <row r="7" ht="160" customHeight="1">
-      <c r="B7" s="17" t="inlineStr">
+      <c r="B7" s="12" t="inlineStr">
         <is>
           <t>3a(i)</t>
         </is>
       </c>
-      <c r="C7" s="19" t="inlineStr">
+      <c r="C7" s="14" t="inlineStr">
         <is>
           <t>The University's Academic Divisions and portfolios support and learn from each other to embed sustainability in practice and in learning – formal, non-formal and informal</t>
         </is>
       </c>
-      <c r="D7" s="19" t="inlineStr">
+      <c r="D7" s="14" t="inlineStr">
         <is>
           <t>List and describe the role of staff focused on sustainability touchstone in Chancellery Education.</t>
         </is>
       </c>
-      <c r="E7" s="19" t="inlineStr">
+      <c r="E7" s="14" t="inlineStr">
         <is>
           <t>Not provided</t>
         </is>
       </c>
-      <c r="F7" s="19" t="inlineStr"/>
-      <c r="G7" s="19" t="inlineStr"/>
-      <c r="H7" s="19" t="inlineStr">
+      <c r="F7" s="14" t="inlineStr"/>
+      <c r="G7" s="14" t="inlineStr"/>
+      <c r="H7" s="14" t="inlineStr">
         <is>
           <t>As per mid-2025: this is not relevant to Ed portfolio. Suggest removing.</t>
         </is>
       </c>
-      <c r="I7" s="19" t="inlineStr"/>
+      <c r="I7" s="14" t="inlineStr"/>
     </row>
     <row r="8" ht="160" customHeight="1">
-      <c r="B8" s="17" t="inlineStr">
+      <c r="B8" s="12" t="inlineStr">
         <is>
           <t>3a(ii)</t>
         </is>
       </c>
-      <c r="C8" s="19" t="inlineStr">
+      <c r="C8" s="14" t="inlineStr">
         <is>
           <t>The University's Academic Divisions and portfolios support and learn from each other to embed sustainability in practice and in learning – formal, non-formal and informal</t>
         </is>
       </c>
-      <c r="D8" s="19" t="inlineStr">
+      <c r="D8" s="14" t="inlineStr">
         <is>
           <t>List and describe any sustainability-focused communities of practice in the Portfolio; their purpose, activities and outcomes.</t>
         </is>
       </c>
-      <c r="E8" s="19" t="inlineStr">
+      <c r="E8" s="14" t="inlineStr">
         <is>
           <t>Not provided</t>
         </is>
       </c>
-      <c r="F8" s="19" t="inlineStr"/>
-      <c r="G8" s="19" t="inlineStr"/>
-      <c r="H8" s="19" t="inlineStr">
+      <c r="F8" s="14" t="inlineStr"/>
+      <c r="G8" s="14" t="inlineStr"/>
+      <c r="H8" s="14" t="inlineStr">
         <is>
           <t>As per mid-2025: this is not relevant to Ed portfolio. Suggest removing.</t>
         </is>
       </c>
-      <c r="I8" s="19" t="inlineStr">
+      <c r="I8" s="14" t="inlineStr">
         <is>
           <t>EN1(c)</t>
         </is>
       </c>
     </row>
     <row r="9" ht="160" customHeight="1">
-      <c r="B9" s="17" t="inlineStr">
+      <c r="B9" s="12" t="inlineStr">
         <is>
           <t>3d(ii)</t>
         </is>
       </c>
-      <c r="C9" s="19" t="inlineStr">
+      <c r="C9" s="14" t="inlineStr">
         <is>
           <t>Academic and professional staff have increased their participation in and contribution to formal and non_x0002_formal learning to develop their general and role-specific sustainability skills</t>
         </is>
       </c>
-      <c r="D9" s="19" t="inlineStr">
+      <c r="D9" s="14" t="inlineStr">
         <is>
           <t>Number of professional staff who have undertaken professional development related to Education for Sustainability</t>
         </is>
       </c>
-      <c r="E9" s="19" t="inlineStr">
+      <c r="E9" s="14" t="inlineStr">
         <is>
           <t>Not provided</t>
         </is>
       </c>
-      <c r="F9" s="19" t="inlineStr"/>
-      <c r="G9" s="19" t="inlineStr"/>
-      <c r="H9" s="19" t="inlineStr">
+      <c r="F9" s="14" t="inlineStr"/>
+      <c r="G9" s="14" t="inlineStr"/>
+      <c r="H9" s="14" t="inlineStr">
         <is>
           <t>As per mid-2025: this is not relevant to Ed portfolio. Suggest removing.</t>
         </is>
       </c>
-      <c r="I9" s="19" t="inlineStr"/>
+      <c r="I9" s="14" t="inlineStr"/>
     </row>
     <row r="10" ht="160" customHeight="1">
-      <c r="B10" s="17" t="inlineStr">
+      <c r="B10" s="12" t="inlineStr">
         <is>
           <t>4a(ii)</t>
         </is>
       </c>
-      <c r="C10" s="19" t="inlineStr">
+      <c r="C10" s="14" t="inlineStr">
         <is>
           <t>Sustainability is integrated into curriculum to an extent that conscientiously extends, beyond a base threshold, each discipline’s (and associated professions/industries’) knowledge of the helpful and harmful impacts it has for the environmental and human systems we depend on</t>
         </is>
       </c>
-      <c r="D10" s="19" t="inlineStr">
+      <c r="D10" s="14" t="inlineStr">
         <is>
           <t>Describe work in Chancellery Education in 2025 related to the sustainability touchstone in the Advancing Students and Education strategy</t>
         </is>
       </c>
-      <c r="E10" s="19" t="inlineStr">
+      <c r="E10" s="14" t="inlineStr">
         <is>
           <t>Not yet started</t>
         </is>
       </c>
-      <c r="F10" s="19" t="inlineStr">
+      <c r="F10" s="14" t="inlineStr">
         <is>
           <t>The Joining Melbourne Module on sustainability is available to all commencing undergraduate students, and several Discovery subjects (completed by all commencing undergraduate students) embed sustainability themes. Work on embedded sustainability within the curriculum is underway at the faculty-level despite the unfunded nature of the sustainability touchstone work planned within ASE.</t>
         </is>
       </c>
-      <c r="G10" s="19" t="inlineStr"/>
-      <c r="H10" s="19" t="inlineStr">
+      <c r="G10" s="14" t="inlineStr"/>
+      <c r="H10" s="14" t="inlineStr">
         <is>
           <t>As per mid-2025: this is unfunded (including new curriculum management system). Faculties are pursuing this but central efforts are on hold.</t>
         </is>
       </c>
-      <c r="I10" s="19" t="inlineStr">
+      <c r="I10" s="14" t="inlineStr">
         <is>
           <t>EE1(a)</t>
         </is>
       </c>
     </row>
     <row r="11" ht="160" customHeight="1">
-      <c r="B11" s="17" t="inlineStr">
+      <c r="B11" s="12" t="inlineStr">
         <is>
           <t>4b(i)</t>
         </is>
       </c>
-      <c r="C11" s="19" t="inlineStr">
+      <c r="C11" s="14" t="inlineStr">
         <is>
           <t>Graduates have increased capabilities to shape, lead and succeed in the careers, communities and industries of sustainable societies (year on year).</t>
         </is>
       </c>
-      <c r="D11" s="19" t="inlineStr">
+      <c r="D11" s="14" t="inlineStr">
         <is>
           <t>Is there any way to measure graduate outcomes related to sustainability in Chancellery Education? If so, please describe.</t>
         </is>
       </c>
-      <c r="E11" s="19" t="inlineStr">
+      <c r="E11" s="14" t="inlineStr">
         <is>
           <t>Not yet started</t>
         </is>
       </c>
-      <c r="F11" s="19" t="inlineStr">
+      <c r="F11" s="14" t="inlineStr">
         <is>
           <t>Facukty work in this area has continued across the University, as has work in co-curricular programs such as Melbourne Plus (see SASS respose, below). These continue to build and enhance graduate capabilities.</t>
         </is>
       </c>
-      <c r="G11" s="19" t="inlineStr"/>
-      <c r="H11" s="19" t="inlineStr">
+      <c r="G11" s="14" t="inlineStr"/>
+      <c r="H11" s="14" t="inlineStr">
         <is>
           <t>As per mid-2025: this is unfunded (including new curriculum management system). Faculties are pursuing this but central efforts are on hold.</t>
         </is>
       </c>
-      <c r="I11" s="19" t="inlineStr"/>
+      <c r="I11" s="14" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -1512,13 +1409,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B1:I9"/>
+  <dimension ref="B1:E9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="B1" t="inlineStr">
         <is>
-          <t>End 2026 target status</t>
+          <t>(not used – no target status rating in 2026)</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
@@ -1534,21 +1431,6 @@
       <c r="E1" t="inlineStr">
         <is>
           <t>Y/N</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>Target status</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>Score</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>Response count</t>
         </is>
       </c>
     </row>
@@ -1573,24 +1455,8 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>Met or exceeded</t>
-        </is>
-      </c>
-      <c r="H2" t="n">
-        <v>3</v>
-      </c>
-      <c r="I2" t="n">
-        <v>1</v>
-      </c>
     </row>
     <row r="3">
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Met or exceeded</t>
-        </is>
-      </c>
       <c r="C3" t="inlineStr">
         <is>
           <t>No</t>
@@ -1606,24 +1472,8 @@
           <t>No</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>Partially met</t>
-        </is>
-      </c>
-      <c r="H3" t="n">
-        <v>2</v>
-      </c>
-      <c r="I3" t="n">
-        <v>1</v>
-      </c>
     </row>
     <row r="4">
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Partially met</t>
-        </is>
-      </c>
       <c r="C4" t="inlineStr">
         <is>
           <t>Partially – see comments</t>
@@ -1639,47 +1489,15 @@
           <t>TBC</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>Not met</t>
-        </is>
-      </c>
-      <c r="H4" t="n">
-        <v>1</v>
-      </c>
-      <c r="I4" t="n">
-        <v>1</v>
-      </c>
     </row>
     <row r="5">
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Not met</t>
-        </is>
-      </c>
       <c r="D5" t="inlineStr">
         <is>
           <t>Received</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>Not yet started</t>
-        </is>
-      </c>
-      <c r="H5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I5" t="n">
-        <v>1</v>
-      </c>
     </row>
     <row r="6">
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Not yet started</t>
-        </is>
-      </c>
       <c r="D6" t="inlineStr">
         <is>
           <t>First review</t>
@@ -1687,11 +1505,6 @@
       </c>
     </row>
     <row r="7">
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Not applicable</t>
-        </is>
-      </c>
       <c r="D7" t="inlineStr">
         <is>
           <t>Follow-up</t>

--- a/output/central_unit_requests/Education - SR26 sustainability reporting request.xlsx
+++ b/output/central_unit_requests/Education - SR26 sustainability reporting request.xlsx
@@ -628,7 +628,7 @@
       </c>
       <c r="B1" s="2" t="inlineStr">
         <is>
-          <t>SR26 sustainability reporting (v0.14)</t>
+          <t>SR26 sustainability reporting (v0.15)</t>
         </is>
       </c>
     </row>

--- a/output/central_unit_requests/Education - SR26 sustainability reporting request.xlsx
+++ b/output/central_unit_requests/Education - SR26 sustainability reporting request.xlsx
@@ -628,7 +628,7 @@
       </c>
       <c r="B1" s="2" t="inlineStr">
         <is>
-          <t>SR26 sustainability reporting (v0.15)</t>
+          <t>SR26 sustainability reporting (v0.16)</t>
         </is>
       </c>
     </row>

--- a/output/central_unit_requests/Education - SR26 sustainability reporting request.xlsx
+++ b/output/central_unit_requests/Education - SR26 sustainability reporting request.xlsx
@@ -20,21 +20,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="18">
+  <fonts count="16">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="Aptos"/>
-      <color rgb="00002060"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <sz val="11"/>
     </font>
     <font>
       <name val="Aptos"/>
@@ -178,61 +170,59 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
       <protection locked="0" hidden="0"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -620,32 +610,22 @@
     <col width="24" customWidth="1" min="17" max="17"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="B1" s="2" t="inlineStr">
-        <is>
-          <t>SR26 sustainability reporting (v0.16)</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="B2" s="3" t="inlineStr">
+    <row r="1"/>
+    <row r="2" ht="39" customHeight="1">
+      <c r="B2" s="1" t="inlineStr">
         <is>
           <t>SR26 sustainability reporting request</t>
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
-      <c r="B4" s="4" t="inlineStr">
+      <c r="B4" s="2" t="inlineStr">
         <is>
           <t>How to use this spreadsheet:</t>
         </is>
       </c>
-      <c r="D4" s="5" t="inlineStr">
+      <c r="D4" s="3" t="inlineStr">
         <is>
           <t>• For each row below, describe progress towards the target (Column L) and/or respond to the 2026 reporting request (Column M)
 • Provide supporting information if required (Column N), including links to documents or images
@@ -661,311 +641,314 @@
     <row r="6"/>
     <row r="7"/>
     <row r="8" ht="60" customHeight="1"/>
-    <row r="11">
-      <c r="B11" s="6" t="inlineStr">
+    <row r="9"/>
+    <row r="10"/>
+    <row r="11" ht="39" customHeight="1">
+      <c r="B11" s="4" t="inlineStr">
         <is>
           <t>Education – Chancellery Education</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="C13" s="7" t="inlineStr">
+    <row r="12"/>
+    <row r="13" ht="27" customHeight="1">
+      <c r="C13" s="5" t="inlineStr">
         <is>
           <t>Sustainability 2030 target and indicator</t>
         </is>
       </c>
-      <c r="H13" s="7" t="inlineStr">
+      <c r="H13" s="5" t="inlineStr">
         <is>
           <t>SR25 response</t>
         </is>
       </c>
-      <c r="L13" s="8" t="inlineStr">
+      <c r="L13" s="6" t="inlineStr">
         <is>
           <t>End-2026 reporting (PLEASE COMPLETE THIS SECTION)</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="B14" s="9" t="inlineStr">
+    <row r="14" ht="60" customHeight="1">
+      <c r="B14" s="7" t="inlineStr">
         <is>
           <t>Ref</t>
         </is>
       </c>
-      <c r="C14" s="9" t="inlineStr">
+      <c r="C14" s="7" t="inlineStr">
         <is>
           <t>Priority area</t>
         </is>
       </c>
-      <c r="D14" s="9" t="inlineStr">
+      <c r="D14" s="7" t="inlineStr">
         <is>
           <t>Sustainability 2030 target</t>
         </is>
       </c>
-      <c r="E14" s="9" t="inlineStr">
+      <c r="E14" s="7" t="inlineStr">
         <is>
           <t>Indicator</t>
         </is>
       </c>
-      <c r="F14" s="9" t="inlineStr">
+      <c r="F14" s="7" t="inlineStr">
         <is>
           <t>2026 Reporting request</t>
         </is>
       </c>
-      <c r="G14" s="9" t="inlineStr">
+      <c r="G14" s="7" t="inlineStr">
         <is>
           <t>How SST will use this data</t>
         </is>
       </c>
-      <c r="H14" s="9" t="inlineStr">
+      <c r="H14" s="7" t="inlineStr">
         <is>
           <t>Related SR25 ref</t>
         </is>
       </c>
-      <c r="I14" s="9" t="inlineStr">
+      <c r="I14" s="7" t="inlineStr">
         <is>
           <t>End-2025 confirmed status</t>
         </is>
       </c>
-      <c r="J14" s="9" t="inlineStr">
+      <c r="J14" s="7" t="inlineStr">
         <is>
           <t>End-2025 reporting response</t>
         </is>
       </c>
-      <c r="K14" s="9" t="inlineStr">
+      <c r="K14" s="7" t="inlineStr">
         <is>
           <t>Links and supporting information</t>
         </is>
       </c>
-      <c r="L14" s="10" t="inlineStr">
+      <c r="L14" s="8" t="inlineStr">
         <is>
           <t>OPTION 1:  Target-level reporting (Column D)</t>
         </is>
       </c>
-      <c r="M14" s="10" t="inlineStr">
+      <c r="M14" s="8" t="inlineStr">
         <is>
           <t>OPTION 2:  Indicator level reporting (Column E/F)</t>
         </is>
       </c>
-      <c r="N14" s="10" t="inlineStr">
+      <c r="N14" s="8" t="inlineStr">
         <is>
           <t>Supporting information/comments</t>
         </is>
       </c>
-      <c r="O14" s="10" t="inlineStr">
+      <c r="O14" s="8" t="inlineStr">
         <is>
           <t>Data source and limitations</t>
         </is>
       </c>
-      <c r="P14" s="10" t="inlineStr">
+      <c r="P14" s="8" t="inlineStr">
         <is>
           <t>Data owner confirms information is accurate</t>
         </is>
       </c>
-      <c r="Q14" s="10" t="inlineStr">
+      <c r="Q14" s="8" t="inlineStr">
         <is>
           <t>Confirmed by (name, role, date)</t>
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="B15" s="11" t="inlineStr"/>
-      <c r="C15" s="11" t="inlineStr"/>
-      <c r="D15" s="11" t="inlineStr"/>
-      <c r="E15" s="11" t="inlineStr"/>
-      <c r="F15" s="11" t="inlineStr"/>
-      <c r="G15" s="11" t="inlineStr"/>
-      <c r="H15" s="11" t="inlineStr"/>
-      <c r="I15" s="11" t="inlineStr"/>
-      <c r="J15" s="11" t="inlineStr"/>
-      <c r="K15" s="11" t="inlineStr"/>
-      <c r="L15" s="11" t="inlineStr">
+    <row r="15" ht="81" customHeight="1">
+      <c r="B15" s="9" t="inlineStr"/>
+      <c r="C15" s="9" t="inlineStr"/>
+      <c r="D15" s="9" t="inlineStr"/>
+      <c r="E15" s="9" t="inlineStr"/>
+      <c r="F15" s="9" t="inlineStr"/>
+      <c r="G15" s="9" t="inlineStr"/>
+      <c r="H15" s="9" t="inlineStr"/>
+      <c r="I15" s="9" t="inlineStr"/>
+      <c r="J15" s="9" t="inlineStr"/>
+      <c r="K15" s="9" t="inlineStr"/>
+      <c r="L15" s="9" t="inlineStr">
         <is>
           <t>A general update on activities in relation to the overarching target (Column D)</t>
         </is>
       </c>
-      <c r="M15" s="11" t="inlineStr">
+      <c r="M15" s="9" t="inlineStr">
         <is>
           <t>Data and commentary in direct response to the reporting request (Column F)</t>
         </is>
       </c>
-      <c r="N15" s="11" t="inlineStr">
+      <c r="N15" s="9" t="inlineStr">
         <is>
           <t>Any additional information (e.g. links, images, documents)</t>
         </is>
       </c>
-      <c r="O15" s="11" t="inlineStr">
+      <c r="O15" s="9" t="inlineStr">
         <is>
           <t>Where did this information come from (system, report, survey, person)? Note any gaps or limitations.</t>
         </is>
       </c>
-      <c r="P15" s="11" t="inlineStr">
+      <c r="P15" s="9" t="inlineStr">
         <is>
           <t>Select 'Yes' to confirm the information provided is accurate and can be used for reporting</t>
         </is>
       </c>
-      <c r="Q15" s="11" t="inlineStr">
+      <c r="Q15" s="9" t="inlineStr">
         <is>
           <t>Name, role and date of the person confirming</t>
         </is>
       </c>
     </row>
-    <row r="16" ht="150" customHeight="1">
-      <c r="B16" s="12" t="inlineStr">
+    <row r="16" ht="204" customHeight="1">
+      <c r="B16" s="10" t="inlineStr">
         <is>
           <t>EE1(a)</t>
         </is>
       </c>
-      <c r="C16" s="13" t="inlineStr">
+      <c r="C16" s="11" t="inlineStr">
         <is>
           <t>Exceptional education</t>
         </is>
       </c>
-      <c r="D16" s="13" t="inlineStr">
+      <c r="D16" s="11" t="inlineStr">
         <is>
           <t>Provide our students with learning experiences that help them build the knowledge, skills and relationships to lead change for sustainable societies.</t>
         </is>
       </c>
-      <c r="E16" s="13" t="inlineStr">
+      <c r="E16" s="11" t="inlineStr">
         <is>
           <t>Evidence of innovative approaches to sustainability teaching and learning</t>
         </is>
       </c>
-      <c r="F16" s="14" t="inlineStr">
+      <c r="F16" s="12" t="inlineStr">
         <is>
           <t>In end-2025 reporting your area reported on the related SP2030 target 4a(ii) (click the ref in Column H to see it in full in Tab 3). Please build on this rather than repeating it, focusing on what is new in 2026.
 Please describe any innovative approaches used within your Faculty/Portfolio to embed sustainability in teaching and learning. This could include examples of subjects, curriculum design, pedagogies, assessment approaches or learning resources. Please provide links or supporting evidence where available.</t>
         </is>
       </c>
-      <c r="G16" s="14" t="inlineStr">
+      <c r="G16" s="12" t="inlineStr">
         <is>
           <t>We will collate examples of sustainability teaching and learning, including experiential and co-curricular learning, across faculties to inform the Exceptional education section of the 2026 Sustainability Report. Strong examples may be followed up for the report.</t>
         </is>
       </c>
-      <c r="H16" s="15" t="inlineStr">
+      <c r="H16" s="13" t="inlineStr">
         <is>
           <t>4a(ii)
 → view SR25 response</t>
         </is>
       </c>
-      <c r="I16" s="14" t="inlineStr">
+      <c r="I16" s="12" t="inlineStr">
         <is>
           <t>Not yet started</t>
         </is>
       </c>
-      <c r="J16" s="14" t="inlineStr">
+      <c r="J16" s="12" t="inlineStr">
         <is>
           <t>The Joining Melbourne Module on sustainability is available to all commencing undergraduate students, and several Discovery subjects (completed by all commencing undergraduate students) embed sustainability themes. Work on embedded sustainability within the curriculum is underway at the faculty-level despite the unfunded nature of the sustainability touchstone work planned within ASE.</t>
         </is>
       </c>
-      <c r="K16" s="14" t="inlineStr">
+      <c r="K16" s="12" t="inlineStr">
         <is>
           <t>As per mid-2025: this is unfunded (including new curriculum management system). Faculties are pursuing this but central efforts are on hold.</t>
         </is>
       </c>
-      <c r="L16" s="16" t="n"/>
-      <c r="M16" s="16" t="n"/>
-      <c r="N16" s="16" t="n"/>
-      <c r="O16" s="16" t="n"/>
-      <c r="P16" s="16" t="n"/>
-      <c r="Q16" s="16" t="n"/>
+      <c r="L16" s="14" t="n"/>
+      <c r="M16" s="14" t="n"/>
+      <c r="N16" s="14" t="n"/>
+      <c r="O16" s="14" t="n"/>
+      <c r="P16" s="14" t="n"/>
+      <c r="Q16" s="14" t="n"/>
     </row>
     <row r="17" ht="150" customHeight="1">
-      <c r="B17" s="12" t="inlineStr">
+      <c r="B17" s="10" t="inlineStr">
         <is>
           <t>EE1(b)</t>
         </is>
       </c>
-      <c r="C17" s="13" t="inlineStr">
+      <c r="C17" s="11" t="inlineStr">
         <is>
           <t>Exceptional education</t>
         </is>
       </c>
-      <c r="D17" s="13" t="inlineStr">
+      <c r="D17" s="11" t="inlineStr">
         <is>
           <t>Provide our students with learning experiences that help them build the knowledge, skills and relationships to lead change for sustainable societies.</t>
         </is>
       </c>
-      <c r="E17" s="13" t="inlineStr">
+      <c r="E17" s="11" t="inlineStr">
         <is>
           <t>Pilots of possible approaches for understanding and developing students’ sustainability self-efficacy</t>
         </is>
       </c>
-      <c r="F17" s="14" t="inlineStr">
+      <c r="F17" s="12" t="inlineStr">
         <is>
           <t>Please describe any pilots or trials undertaken within your Faculty/Portfolio to understand or strengthen students’ sustainability self-efficacy. This could include the approach used, participating cohorts, what was assessed or learned, and any planned next steps.</t>
         </is>
       </c>
-      <c r="G17" s="14" t="inlineStr">
+      <c r="G17" s="12" t="inlineStr">
         <is>
           <t>This is a new indicator. We will use responses to establish a baseline of how (and whether) faculties are understanding student sustainability self-efficacy, and report on early pilots in the 2026 Sustainability Report. A nil response is useful to us.</t>
         </is>
       </c>
-      <c r="H17" s="14" t="inlineStr">
+      <c r="H17" s="12" t="inlineStr">
         <is>
           <t>N/A – new indicator</t>
         </is>
       </c>
-      <c r="I17" s="14" t="inlineStr"/>
-      <c r="J17" s="14" t="inlineStr"/>
-      <c r="K17" s="14" t="inlineStr"/>
-      <c r="L17" s="16" t="n"/>
-      <c r="M17" s="16" t="n"/>
-      <c r="N17" s="16" t="n"/>
-      <c r="O17" s="16" t="n"/>
-      <c r="P17" s="16" t="n"/>
-      <c r="Q17" s="16" t="n"/>
-    </row>
-    <row r="18" ht="150" customHeight="1">
-      <c r="B18" s="12" t="inlineStr">
+      <c r="I17" s="12" t="inlineStr"/>
+      <c r="J17" s="12" t="inlineStr"/>
+      <c r="K17" s="12" t="inlineStr"/>
+      <c r="L17" s="14" t="n"/>
+      <c r="M17" s="14" t="n"/>
+      <c r="N17" s="14" t="n"/>
+      <c r="O17" s="14" t="n"/>
+      <c r="P17" s="14" t="n"/>
+      <c r="Q17" s="14" t="n"/>
+    </row>
+    <row r="18" ht="171" customHeight="1">
+      <c r="B18" s="10" t="inlineStr">
         <is>
           <t>EN1(c)</t>
         </is>
       </c>
-      <c r="C18" s="13" t="inlineStr">
+      <c r="C18" s="11" t="inlineStr">
         <is>
           <t>Enablers</t>
         </is>
       </c>
-      <c r="D18" s="13" t="inlineStr">
+      <c r="D18" s="11" t="inlineStr">
         <is>
           <t>Enablers</t>
         </is>
       </c>
-      <c r="E18" s="13" t="inlineStr">
+      <c r="E18" s="11" t="inlineStr">
         <is>
           <t>Coordinated internal engagement and external partnerships contributing to delivery of sustainability outcomes across priority areas.</t>
         </is>
       </c>
-      <c r="F18" s="14" t="inlineStr">
+      <c r="F18" s="12" t="inlineStr">
         <is>
           <t>We did not receive an end-2025 response for the related SP2030 target 3a(ii), so please include any relevant activity from across 2026.
 Please provide examples of internal engagement or external partnerships involving your Faculty/Portfolio that contributed to Sustainability 2030 outcomes, could include the priority area addressed, participating groups/partners, nature of the collaboration and key outcomes.</t>
         </is>
       </c>
-      <c r="G18" s="14" t="inlineStr">
+      <c r="G18" s="12" t="inlineStr">
         <is>
           <t>We will report on internal engagement and partnerships contributing to Sustainability 2030 outcomes, and update our record of sustainability-focused communities of practice and contacts across the University.</t>
         </is>
       </c>
-      <c r="H18" s="15" t="inlineStr">
+      <c r="H18" s="13" t="inlineStr">
         <is>
           <t>3a(ii)
 → view SR25 response</t>
         </is>
       </c>
-      <c r="I18" s="14" t="inlineStr"/>
-      <c r="J18" s="14" t="inlineStr"/>
-      <c r="K18" s="14" t="inlineStr">
+      <c r="I18" s="12" t="inlineStr"/>
+      <c r="J18" s="12" t="inlineStr"/>
+      <c r="K18" s="12" t="inlineStr">
         <is>
           <t>As per mid-2025: this is not relevant to Ed portfolio. Suggest removing.</t>
         </is>
       </c>
-      <c r="L18" s="16" t="n"/>
-      <c r="M18" s="16" t="n"/>
-      <c r="N18" s="16" t="n"/>
-      <c r="O18" s="16" t="n"/>
-      <c r="P18" s="16" t="n"/>
-      <c r="Q18" s="16" t="n"/>
+      <c r="L18" s="14" t="n"/>
+      <c r="M18" s="14" t="n"/>
+      <c r="N18" s="14" t="n"/>
+      <c r="O18" s="14" t="n"/>
+      <c r="P18" s="14" t="n"/>
+      <c r="Q18" s="14" t="n"/>
     </row>
     <row r="19"/>
   </sheetData>
@@ -1010,110 +993,102 @@
     <col width="30" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="B1" s="2" t="inlineStr">
-        <is>
-          <t>SR26 sustainability reporting</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="B2" s="3" t="inlineStr">
+    <row r="1"/>
+    <row r="2" ht="39" customHeight="1">
+      <c r="B2" s="1" t="inlineStr">
         <is>
           <t>Highlighted stories (optional)</t>
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="B5" s="17" t="inlineStr">
+    <row r="3"/>
+    <row r="4"/>
+    <row r="5" ht="22" customHeight="1">
+      <c r="B5" s="15" t="inlineStr">
         <is>
           <t>How to use this spreadsheet</t>
         </is>
       </c>
-      <c r="C5" s="18" t="inlineStr">
+      <c r="C5" s="16" t="inlineStr">
         <is>
           <t>Please share up to 3 stories from 2026 which highlight your faculty's/portfolio's sustainability progress and/or impact. These stories can directly relate to Sustainability 2030 targets and indicators, or sustainability more generally. Due: Tuesday 15 December 2026 (early submission helps us develop case studies).</t>
         </is>
       </c>
     </row>
     <row r="6"/>
-    <row r="8">
-      <c r="B8" s="19" t="inlineStr">
+    <row r="7"/>
+    <row r="8" ht="39" customHeight="1">
+      <c r="B8" s="17" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="C8" s="19" t="inlineStr">
+      <c r="C8" s="17" t="inlineStr">
         <is>
           <t>Description</t>
         </is>
       </c>
-      <c r="D8" s="19" t="inlineStr">
+      <c r="D8" s="17" t="inlineStr">
         <is>
           <t>Related Sustainability 2030 targets (optional)</t>
         </is>
       </c>
-      <c r="E8" s="19" t="inlineStr">
+      <c r="E8" s="17" t="inlineStr">
         <is>
           <t>Images and other media</t>
         </is>
       </c>
-      <c r="F8" s="19" t="inlineStr">
+      <c r="F8" s="17" t="inlineStr">
         <is>
           <t>Links and supporting documentation</t>
         </is>
       </c>
     </row>
     <row r="9" ht="90" customHeight="1">
-      <c r="B9" s="20" t="inlineStr"/>
-      <c r="C9" s="20" t="inlineStr">
+      <c r="B9" s="18" t="inlineStr"/>
+      <c r="C9" s="18" t="inlineStr">
         <is>
           <t>• Please include a brief description of a project or activity that has made a significant contribution to sustainability at the University (up to 250 words)
 • Summarise the benefits. Benefits may relate to operational outcomes, environmental/social outcomes, and sector benefits.</t>
         </is>
       </c>
-      <c r="D9" s="20" t="inlineStr"/>
-      <c r="E9" s="20" t="inlineStr">
+      <c r="D9" s="18" t="inlineStr"/>
+      <c r="E9" s="18" t="inlineStr">
         <is>
           <t>(link to OneDrive/SharePoint files or published online content preferred)</t>
         </is>
       </c>
-      <c r="F9" s="20" t="inlineStr"/>
+      <c r="F9" s="18" t="inlineStr"/>
     </row>
     <row r="10" ht="120" customHeight="1">
       <c r="A10" t="n">
         <v>1</v>
       </c>
-      <c r="B10" s="16" t="n"/>
-      <c r="C10" s="16" t="n"/>
-      <c r="D10" s="16" t="n"/>
-      <c r="E10" s="16" t="n"/>
-      <c r="F10" s="16" t="n"/>
+      <c r="B10" s="14" t="n"/>
+      <c r="C10" s="14" t="n"/>
+      <c r="D10" s="14" t="n"/>
+      <c r="E10" s="14" t="n"/>
+      <c r="F10" s="14" t="n"/>
     </row>
     <row r="11" ht="120" customHeight="1">
       <c r="A11" t="n">
         <v>2</v>
       </c>
-      <c r="B11" s="16" t="n"/>
-      <c r="C11" s="16" t="n"/>
-      <c r="D11" s="16" t="n"/>
-      <c r="E11" s="16" t="n"/>
-      <c r="F11" s="16" t="n"/>
+      <c r="B11" s="14" t="n"/>
+      <c r="C11" s="14" t="n"/>
+      <c r="D11" s="14" t="n"/>
+      <c r="E11" s="14" t="n"/>
+      <c r="F11" s="14" t="n"/>
     </row>
     <row r="12" ht="120" customHeight="1">
       <c r="A12" t="n">
         <v>3</v>
       </c>
-      <c r="B12" s="16" t="n"/>
-      <c r="C12" s="16" t="n"/>
-      <c r="D12" s="16" t="n"/>
-      <c r="E12" s="16" t="n"/>
-      <c r="F12" s="16" t="n"/>
+      <c r="B12" s="14" t="n"/>
+      <c r="C12" s="14" t="n"/>
+      <c r="D12" s="14" t="n"/>
+      <c r="E12" s="14" t="n"/>
+      <c r="F12" s="14" t="n"/>
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="1"/>
@@ -1144,253 +1119,242 @@
     <col width="16" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="B1" s="2" t="inlineStr">
-        <is>
-          <t>End-2025 target status assessment and reporting (for reference)</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="B2" s="3" t="inlineStr">
+    <row r="1"/>
+    <row r="2" ht="39" customHeight="1">
+      <c r="B2" s="1" t="inlineStr">
         <is>
           <t>Your SR25 responses – Chancellery Education</t>
         </is>
       </c>
     </row>
     <row r="3" ht="32" customHeight="1">
-      <c r="B3" s="18" t="inlineStr">
+      <c r="B3" s="16" t="inlineStr">
         <is>
           <t>Your responses to the end-2025 reporting request, against the former Sustainability Plan 2030 (SP2030) targets. For reference only – please do not edit. Use the 'Back to request' links to return to the reporting template.</t>
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="B4" s="21" t="inlineStr">
+    <row r="4" ht="22" customHeight="1">
+      <c r="B4" s="19" t="inlineStr">
         <is>
           <t>← Back to request</t>
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="B5" s="22" t="inlineStr">
+    <row r="5" ht="30" customHeight="1">
+      <c r="B5" s="20" t="inlineStr">
         <is>
           <t>Chancellery Education</t>
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="B6" s="9" t="inlineStr">
+    <row r="6" ht="42" customHeight="1">
+      <c r="B6" s="7" t="inlineStr">
         <is>
           <t>SR25 ref</t>
         </is>
       </c>
-      <c r="C6" s="9" t="inlineStr">
+      <c r="C6" s="7" t="inlineStr">
         <is>
           <t>SP2030 target</t>
         </is>
       </c>
-      <c r="D6" s="9" t="inlineStr">
+      <c r="D6" s="7" t="inlineStr">
         <is>
           <t>2025 reporting request</t>
         </is>
       </c>
-      <c r="E6" s="9" t="inlineStr">
+      <c r="E6" s="7" t="inlineStr">
         <is>
           <t>Confirmed end-2025 status</t>
         </is>
       </c>
-      <c r="F6" s="9" t="inlineStr">
+      <c r="F6" s="7" t="inlineStr">
         <is>
           <t>OPTION 1: Target-level reporting</t>
         </is>
       </c>
-      <c r="G6" s="9" t="inlineStr">
+      <c r="G6" s="7" t="inlineStr">
         <is>
           <t>OPTION 2: Indicator-level reporting</t>
         </is>
       </c>
-      <c r="H6" s="9" t="inlineStr">
+      <c r="H6" s="7" t="inlineStr">
         <is>
           <t>Supporting information/comments</t>
         </is>
       </c>
-      <c r="I6" s="9" t="inlineStr">
+      <c r="I6" s="7" t="inlineStr">
         <is>
           <t>Related SR26 indicator(s)</t>
         </is>
       </c>
     </row>
     <row r="7" ht="160" customHeight="1">
-      <c r="B7" s="12" t="inlineStr">
+      <c r="B7" s="10" t="inlineStr">
         <is>
           <t>3a(i)</t>
         </is>
       </c>
-      <c r="C7" s="14" t="inlineStr">
+      <c r="C7" s="12" t="inlineStr">
         <is>
           <t>The University's Academic Divisions and portfolios support and learn from each other to embed sustainability in practice and in learning – formal, non-formal and informal</t>
         </is>
       </c>
-      <c r="D7" s="14" t="inlineStr">
+      <c r="D7" s="12" t="inlineStr">
         <is>
           <t>List and describe the role of staff focused on sustainability touchstone in Chancellery Education.</t>
         </is>
       </c>
-      <c r="E7" s="14" t="inlineStr">
+      <c r="E7" s="12" t="inlineStr">
         <is>
           <t>Not provided</t>
         </is>
       </c>
-      <c r="F7" s="14" t="inlineStr"/>
-      <c r="G7" s="14" t="inlineStr"/>
-      <c r="H7" s="14" t="inlineStr">
+      <c r="F7" s="12" t="inlineStr"/>
+      <c r="G7" s="12" t="inlineStr"/>
+      <c r="H7" s="12" t="inlineStr">
         <is>
           <t>As per mid-2025: this is not relevant to Ed portfolio. Suggest removing.</t>
         </is>
       </c>
-      <c r="I7" s="14" t="inlineStr"/>
+      <c r="I7" s="12" t="inlineStr"/>
     </row>
     <row r="8" ht="160" customHeight="1">
-      <c r="B8" s="12" t="inlineStr">
+      <c r="B8" s="10" t="inlineStr">
         <is>
           <t>3a(ii)</t>
         </is>
       </c>
-      <c r="C8" s="14" t="inlineStr">
+      <c r="C8" s="12" t="inlineStr">
         <is>
           <t>The University's Academic Divisions and portfolios support and learn from each other to embed sustainability in practice and in learning – formal, non-formal and informal</t>
         </is>
       </c>
-      <c r="D8" s="14" t="inlineStr">
+      <c r="D8" s="12" t="inlineStr">
         <is>
           <t>List and describe any sustainability-focused communities of practice in the Portfolio; their purpose, activities and outcomes.</t>
         </is>
       </c>
-      <c r="E8" s="14" t="inlineStr">
+      <c r="E8" s="12" t="inlineStr">
         <is>
           <t>Not provided</t>
         </is>
       </c>
-      <c r="F8" s="14" t="inlineStr"/>
-      <c r="G8" s="14" t="inlineStr"/>
-      <c r="H8" s="14" t="inlineStr">
+      <c r="F8" s="12" t="inlineStr"/>
+      <c r="G8" s="12" t="inlineStr"/>
+      <c r="H8" s="12" t="inlineStr">
         <is>
           <t>As per mid-2025: this is not relevant to Ed portfolio. Suggest removing.</t>
         </is>
       </c>
-      <c r="I8" s="14" t="inlineStr">
+      <c r="I8" s="12" t="inlineStr">
         <is>
           <t>EN1(c)</t>
         </is>
       </c>
     </row>
     <row r="9" ht="160" customHeight="1">
-      <c r="B9" s="12" t="inlineStr">
+      <c r="B9" s="10" t="inlineStr">
         <is>
           <t>3d(ii)</t>
         </is>
       </c>
-      <c r="C9" s="14" t="inlineStr">
+      <c r="C9" s="12" t="inlineStr">
         <is>
           <t>Academic and professional staff have increased their participation in and contribution to formal and non_x0002_formal learning to develop their general and role-specific sustainability skills</t>
         </is>
       </c>
-      <c r="D9" s="14" t="inlineStr">
+      <c r="D9" s="12" t="inlineStr">
         <is>
           <t>Number of professional staff who have undertaken professional development related to Education for Sustainability</t>
         </is>
       </c>
-      <c r="E9" s="14" t="inlineStr">
+      <c r="E9" s="12" t="inlineStr">
         <is>
           <t>Not provided</t>
         </is>
       </c>
-      <c r="F9" s="14" t="inlineStr"/>
-      <c r="G9" s="14" t="inlineStr"/>
-      <c r="H9" s="14" t="inlineStr">
+      <c r="F9" s="12" t="inlineStr"/>
+      <c r="G9" s="12" t="inlineStr"/>
+      <c r="H9" s="12" t="inlineStr">
         <is>
           <t>As per mid-2025: this is not relevant to Ed portfolio. Suggest removing.</t>
         </is>
       </c>
-      <c r="I9" s="14" t="inlineStr"/>
+      <c r="I9" s="12" t="inlineStr"/>
     </row>
     <row r="10" ht="160" customHeight="1">
-      <c r="B10" s="12" t="inlineStr">
+      <c r="B10" s="10" t="inlineStr">
         <is>
           <t>4a(ii)</t>
         </is>
       </c>
-      <c r="C10" s="14" t="inlineStr">
+      <c r="C10" s="12" t="inlineStr">
         <is>
           <t>Sustainability is integrated into curriculum to an extent that conscientiously extends, beyond a base threshold, each discipline’s (and associated professions/industries’) knowledge of the helpful and harmful impacts it has for the environmental and human systems we depend on</t>
         </is>
       </c>
-      <c r="D10" s="14" t="inlineStr">
+      <c r="D10" s="12" t="inlineStr">
         <is>
           <t>Describe work in Chancellery Education in 2025 related to the sustainability touchstone in the Advancing Students and Education strategy</t>
         </is>
       </c>
-      <c r="E10" s="14" t="inlineStr">
+      <c r="E10" s="12" t="inlineStr">
         <is>
           <t>Not yet started</t>
         </is>
       </c>
-      <c r="F10" s="14" t="inlineStr">
+      <c r="F10" s="12" t="inlineStr">
         <is>
           <t>The Joining Melbourne Module on sustainability is available to all commencing undergraduate students, and several Discovery subjects (completed by all commencing undergraduate students) embed sustainability themes. Work on embedded sustainability within the curriculum is underway at the faculty-level despite the unfunded nature of the sustainability touchstone work planned within ASE.</t>
         </is>
       </c>
-      <c r="G10" s="14" t="inlineStr"/>
-      <c r="H10" s="14" t="inlineStr">
+      <c r="G10" s="12" t="inlineStr"/>
+      <c r="H10" s="12" t="inlineStr">
         <is>
           <t>As per mid-2025: this is unfunded (including new curriculum management system). Faculties are pursuing this but central efforts are on hold.</t>
         </is>
       </c>
-      <c r="I10" s="14" t="inlineStr">
+      <c r="I10" s="12" t="inlineStr">
         <is>
           <t>EE1(a)</t>
         </is>
       </c>
     </row>
     <row r="11" ht="160" customHeight="1">
-      <c r="B11" s="12" t="inlineStr">
+      <c r="B11" s="10" t="inlineStr">
         <is>
           <t>4b(i)</t>
         </is>
       </c>
-      <c r="C11" s="14" t="inlineStr">
+      <c r="C11" s="12" t="inlineStr">
         <is>
           <t>Graduates have increased capabilities to shape, lead and succeed in the careers, communities and industries of sustainable societies (year on year).</t>
         </is>
       </c>
-      <c r="D11" s="14" t="inlineStr">
+      <c r="D11" s="12" t="inlineStr">
         <is>
           <t>Is there any way to measure graduate outcomes related to sustainability in Chancellery Education? If so, please describe.</t>
         </is>
       </c>
-      <c r="E11" s="14" t="inlineStr">
+      <c r="E11" s="12" t="inlineStr">
         <is>
           <t>Not yet started</t>
         </is>
       </c>
-      <c r="F11" s="14" t="inlineStr">
+      <c r="F11" s="12" t="inlineStr">
         <is>
           <t>Facukty work in this area has continued across the University, as has work in co-curricular programs such as Melbourne Plus (see SASS respose, below). These continue to build and enhance graduate capabilities.</t>
         </is>
       </c>
-      <c r="G11" s="14" t="inlineStr"/>
-      <c r="H11" s="14" t="inlineStr">
+      <c r="G11" s="12" t="inlineStr"/>
+      <c r="H11" s="12" t="inlineStr">
         <is>
           <t>As per mid-2025: this is unfunded (including new curriculum management system). Faculties are pursuing this but central efforts are on hold.</t>
         </is>
       </c>
-      <c r="I11" s="14" t="inlineStr"/>
+      <c r="I11" s="12" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -1409,10 +1373,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B1:E9"/>
+  <dimension ref="A1:E9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="13" customWidth="1" min="1" max="1"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
+  </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="22" customHeight="1">
       <c r="B1" t="inlineStr">
         <is>
           <t>(not used – no target status rating in 2026)</t>
@@ -1434,7 +1405,7 @@
         </is>
       </c>
     </row>
-    <row r="2">
+    <row r="2" ht="22" customHeight="1">
       <c r="B2" t="inlineStr">
         <is>
           <t>Please select from dropdown</t>
@@ -1456,7 +1427,7 @@
         </is>
       </c>
     </row>
-    <row r="3">
+    <row r="3" ht="22" customHeight="1">
       <c r="C3" t="inlineStr">
         <is>
           <t>No</t>
@@ -1473,7 +1444,7 @@
         </is>
       </c>
     </row>
-    <row r="4">
+    <row r="4" ht="22" customHeight="1">
       <c r="C4" t="inlineStr">
         <is>
           <t>Partially – see comments</t>
@@ -1490,35 +1461,35 @@
         </is>
       </c>
     </row>
-    <row r="5">
+    <row r="5" ht="22" customHeight="1">
       <c r="D5" t="inlineStr">
         <is>
           <t>Received</t>
         </is>
       </c>
     </row>
-    <row r="6">
+    <row r="6" ht="22" customHeight="1">
       <c r="D6" t="inlineStr">
         <is>
           <t>First review</t>
         </is>
       </c>
     </row>
-    <row r="7">
+    <row r="7" ht="22" customHeight="1">
       <c r="D7" t="inlineStr">
         <is>
           <t>Follow-up</t>
         </is>
       </c>
     </row>
-    <row r="8">
+    <row r="8" ht="22" customHeight="1">
       <c r="D8" t="inlineStr">
         <is>
           <t>Complete</t>
         </is>
       </c>
     </row>
-    <row r="9">
+    <row r="9" ht="22" customHeight="1">
       <c r="D9" t="inlineStr">
         <is>
           <t>Not required</t>

--- a/output/central_unit_requests/Education - SR26 sustainability reporting request.xlsx
+++ b/output/central_unit_requests/Education - SR26 sustainability reporting request.xlsx
@@ -633,7 +633,7 @@
 • Where a related end-2025 target existed, click the ref in Column H to see your full SR25 response (Tab 3)
 • Use Tab 2 of this spreadsheet to highlight key sustainability stories (optional)
 • 2026 is a transition year: Sustainability 2030 launched ~20 October 2026, so report on activity across all of 2026 and any early actions since launch. No target status rating is requested this year.
-• Due: Tuesday 15 December 2026. Questions: CDSS – questions and clarifications are recorded centrally (contact email TBC); optional 1:1 meetings available on request</t>
+• Due: Tuesday 15 December 2026. Questions: Sustainability Strategy team (SST) – questions and clarifications are recorded centrally (contact email TBC); optional 1:1 meetings available on request</t>
         </is>
       </c>
     </row>

--- a/output/central_unit_requests/Education - SR26 sustainability reporting request.xlsx
+++ b/output/central_unit_requests/Education - SR26 sustainability reporting request.xlsx
@@ -31,7 +31,7 @@
     <font>
       <name val="Aptos"/>
       <b val="1"/>
-      <color rgb="00002060"/>
+      <color rgb="00FFFFFF"/>
       <sz val="22"/>
     </font>
     <font>
@@ -110,7 +110,7 @@
       <b val="1"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
@@ -135,6 +135,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00FFC000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00000F46"/>
       </patternFill>
     </fill>
   </fills>
@@ -170,9 +175,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" indent="4"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -297,6 +305,96 @@
     </indexedColors>
   </colors>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>57150</colOff>
+      <row>1</row>
+      <rowOff>57150</rowOff>
+    </from>
+    <ext cx="609600" cy="609600"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>57150</colOff>
+      <row>1</row>
+      <rowOff>57150</rowOff>
+    </from>
+    <ext cx="609600" cy="609600"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>57150</colOff>
+      <row>1</row>
+      <rowOff>57150</rowOff>
+    </from>
+    <ext cx="609600" cy="609600"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -588,7 +686,7 @@
     <outlinePr summaryBelow="1" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q19"/>
+  <dimension ref="A1:R19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -608,24 +706,61 @@
     <col width="30" customWidth="1" min="15" max="15"/>
     <col width="20" customWidth="1" min="16" max="16"/>
     <col width="24" customWidth="1" min="17" max="17"/>
+    <col width="13" customWidth="1" min="18" max="18"/>
   </cols>
   <sheetData>
-    <row r="1"/>
-    <row r="2" ht="39" customHeight="1">
-      <c r="B2" s="1" t="inlineStr">
+    <row r="1" ht="8" customHeight="1">
+      <c r="A1" s="1" t="n"/>
+      <c r="B1" s="1" t="n"/>
+      <c r="C1" s="1" t="n"/>
+      <c r="D1" s="1" t="n"/>
+      <c r="E1" s="1" t="n"/>
+      <c r="F1" s="1" t="n"/>
+      <c r="G1" s="1" t="n"/>
+      <c r="H1" s="1" t="n"/>
+      <c r="I1" s="1" t="n"/>
+      <c r="J1" s="1" t="n"/>
+      <c r="K1" s="1" t="n"/>
+      <c r="L1" s="1" t="n"/>
+      <c r="M1" s="1" t="n"/>
+      <c r="N1" s="1" t="n"/>
+      <c r="O1" s="1" t="n"/>
+      <c r="P1" s="1" t="n"/>
+      <c r="Q1" s="1" t="n"/>
+      <c r="R1" s="1" t="n"/>
+    </row>
+    <row r="2" ht="58" customHeight="1">
+      <c r="A2" s="1" t="n"/>
+      <c r="B2" s="2" t="inlineStr">
         <is>
           <t>SR26 sustainability reporting request</t>
         </is>
       </c>
+      <c r="C2" s="1" t="n"/>
+      <c r="D2" s="1" t="n"/>
+      <c r="E2" s="1" t="n"/>
+      <c r="F2" s="1" t="n"/>
+      <c r="G2" s="1" t="n"/>
+      <c r="H2" s="1" t="n"/>
+      <c r="I2" s="1" t="n"/>
+      <c r="J2" s="1" t="n"/>
+      <c r="K2" s="1" t="n"/>
+      <c r="L2" s="1" t="n"/>
+      <c r="M2" s="1" t="n"/>
+      <c r="N2" s="1" t="n"/>
+      <c r="O2" s="1" t="n"/>
+      <c r="P2" s="1" t="n"/>
+      <c r="Q2" s="1" t="n"/>
+      <c r="R2" s="1" t="n"/>
     </row>
     <row r="3"/>
     <row r="4">
-      <c r="B4" s="2" t="inlineStr">
+      <c r="B4" s="3" t="inlineStr">
         <is>
           <t>How to use this spreadsheet:</t>
         </is>
       </c>
-      <c r="D4" s="3" t="inlineStr">
+      <c r="D4" s="4" t="inlineStr">
         <is>
           <t>• For each row below, describe progress towards the target (Column L) and/or respond to the 2026 reporting request (Column M)
 • Provide supporting information if required (Column N), including links to documents or images
@@ -633,7 +768,7 @@
 • Where a related end-2025 target existed, click the ref in Column H to see your full SR25 response (Tab 3)
 • Use Tab 2 of this spreadsheet to highlight key sustainability stories (optional)
 • 2026 is a transition year: Sustainability 2030 launched ~20 October 2026, so report on activity across all of 2026 and any early actions since launch. No target status rating is requested this year.
-• Due: Tuesday 15 December 2026. Questions: Sustainability Strategy team (SST) – questions and clarifications are recorded centrally (contact email TBC); optional 1:1 meetings available on request</t>
+• Due: Thursday 24 December 2026 (Christmas shutdown). Questions: Sustainability Strategy team (SST) – questions and clarifications are recorded centrally (contact email TBC); optional 1:1 meetings available on request</t>
         </is>
       </c>
     </row>
@@ -644,7 +779,7 @@
     <row r="9"/>
     <row r="10"/>
     <row r="11" ht="39" customHeight="1">
-      <c r="B11" s="4" t="inlineStr">
+      <c r="B11" s="5" t="inlineStr">
         <is>
           <t>Education – Chancellery Education</t>
         </is>
@@ -652,303 +787,303 @@
     </row>
     <row r="12"/>
     <row r="13" ht="27" customHeight="1">
-      <c r="C13" s="5" t="inlineStr">
+      <c r="C13" s="6" t="inlineStr">
         <is>
           <t>Sustainability 2030 target and indicator</t>
         </is>
       </c>
-      <c r="H13" s="5" t="inlineStr">
+      <c r="H13" s="6" t="inlineStr">
         <is>
           <t>SR25 response</t>
         </is>
       </c>
-      <c r="L13" s="6" t="inlineStr">
+      <c r="L13" s="7" t="inlineStr">
         <is>
           <t>End-2026 reporting (PLEASE COMPLETE THIS SECTION)</t>
         </is>
       </c>
     </row>
     <row r="14" ht="60" customHeight="1">
-      <c r="B14" s="7" t="inlineStr">
+      <c r="B14" s="8" t="inlineStr">
         <is>
           <t>Ref</t>
         </is>
       </c>
-      <c r="C14" s="7" t="inlineStr">
+      <c r="C14" s="8" t="inlineStr">
         <is>
           <t>Priority area</t>
         </is>
       </c>
-      <c r="D14" s="7" t="inlineStr">
+      <c r="D14" s="8" t="inlineStr">
         <is>
           <t>Sustainability 2030 target</t>
         </is>
       </c>
-      <c r="E14" s="7" t="inlineStr">
+      <c r="E14" s="8" t="inlineStr">
         <is>
           <t>Indicator</t>
         </is>
       </c>
-      <c r="F14" s="7" t="inlineStr">
+      <c r="F14" s="8" t="inlineStr">
         <is>
           <t>2026 Reporting request</t>
         </is>
       </c>
-      <c r="G14" s="7" t="inlineStr">
+      <c r="G14" s="8" t="inlineStr">
         <is>
           <t>How SST will use this data</t>
         </is>
       </c>
-      <c r="H14" s="7" t="inlineStr">
+      <c r="H14" s="8" t="inlineStr">
         <is>
           <t>Related SR25 ref</t>
         </is>
       </c>
-      <c r="I14" s="7" t="inlineStr">
+      <c r="I14" s="8" t="inlineStr">
         <is>
           <t>End-2025 confirmed status</t>
         </is>
       </c>
-      <c r="J14" s="7" t="inlineStr">
+      <c r="J14" s="8" t="inlineStr">
         <is>
           <t>End-2025 reporting response</t>
         </is>
       </c>
-      <c r="K14" s="7" t="inlineStr">
+      <c r="K14" s="8" t="inlineStr">
         <is>
           <t>Links and supporting information</t>
         </is>
       </c>
-      <c r="L14" s="8" t="inlineStr">
+      <c r="L14" s="9" t="inlineStr">
         <is>
           <t>OPTION 1:  Target-level reporting (Column D)</t>
         </is>
       </c>
-      <c r="M14" s="8" t="inlineStr">
+      <c r="M14" s="9" t="inlineStr">
         <is>
           <t>OPTION 2:  Indicator level reporting (Column E/F)</t>
         </is>
       </c>
-      <c r="N14" s="8" t="inlineStr">
+      <c r="N14" s="9" t="inlineStr">
         <is>
           <t>Supporting information/comments</t>
         </is>
       </c>
-      <c r="O14" s="8" t="inlineStr">
+      <c r="O14" s="9" t="inlineStr">
         <is>
           <t>Data source and limitations</t>
         </is>
       </c>
-      <c r="P14" s="8" t="inlineStr">
+      <c r="P14" s="9" t="inlineStr">
         <is>
           <t>Data owner confirms information is accurate</t>
         </is>
       </c>
-      <c r="Q14" s="8" t="inlineStr">
+      <c r="Q14" s="9" t="inlineStr">
         <is>
           <t>Confirmed by (name, role, date)</t>
         </is>
       </c>
     </row>
     <row r="15" ht="81" customHeight="1">
-      <c r="B15" s="9" t="inlineStr"/>
-      <c r="C15" s="9" t="inlineStr"/>
-      <c r="D15" s="9" t="inlineStr"/>
-      <c r="E15" s="9" t="inlineStr"/>
-      <c r="F15" s="9" t="inlineStr"/>
-      <c r="G15" s="9" t="inlineStr"/>
-      <c r="H15" s="9" t="inlineStr"/>
-      <c r="I15" s="9" t="inlineStr"/>
-      <c r="J15" s="9" t="inlineStr"/>
-      <c r="K15" s="9" t="inlineStr"/>
-      <c r="L15" s="9" t="inlineStr">
+      <c r="B15" s="10" t="inlineStr"/>
+      <c r="C15" s="10" t="inlineStr"/>
+      <c r="D15" s="10" t="inlineStr"/>
+      <c r="E15" s="10" t="inlineStr"/>
+      <c r="F15" s="10" t="inlineStr"/>
+      <c r="G15" s="10" t="inlineStr"/>
+      <c r="H15" s="10" t="inlineStr"/>
+      <c r="I15" s="10" t="inlineStr"/>
+      <c r="J15" s="10" t="inlineStr"/>
+      <c r="K15" s="10" t="inlineStr"/>
+      <c r="L15" s="10" t="inlineStr">
         <is>
           <t>A general update on activities in relation to the overarching target (Column D)</t>
         </is>
       </c>
-      <c r="M15" s="9" t="inlineStr">
+      <c r="M15" s="10" t="inlineStr">
         <is>
           <t>Data and commentary in direct response to the reporting request (Column F)</t>
         </is>
       </c>
-      <c r="N15" s="9" t="inlineStr">
+      <c r="N15" s="10" t="inlineStr">
         <is>
           <t>Any additional information (e.g. links, images, documents)</t>
         </is>
       </c>
-      <c r="O15" s="9" t="inlineStr">
+      <c r="O15" s="10" t="inlineStr">
         <is>
           <t>Where did this information come from (system, report, survey, person)? Note any gaps or limitations.</t>
         </is>
       </c>
-      <c r="P15" s="9" t="inlineStr">
+      <c r="P15" s="10" t="inlineStr">
         <is>
           <t>Select 'Yes' to confirm the information provided is accurate and can be used for reporting</t>
         </is>
       </c>
-      <c r="Q15" s="9" t="inlineStr">
+      <c r="Q15" s="10" t="inlineStr">
         <is>
           <t>Name, role and date of the person confirming</t>
         </is>
       </c>
     </row>
-    <row r="16" ht="204" customHeight="1">
-      <c r="B16" s="10" t="inlineStr">
+    <row r="16" ht="171" customHeight="1">
+      <c r="B16" s="11" t="inlineStr">
         <is>
           <t>EE1(a)</t>
         </is>
       </c>
-      <c r="C16" s="11" t="inlineStr">
+      <c r="C16" s="12" t="inlineStr">
         <is>
           <t>Exceptional education</t>
         </is>
       </c>
-      <c r="D16" s="11" t="inlineStr">
+      <c r="D16" s="12" t="inlineStr">
         <is>
           <t>Provide our students with learning experiences that help them build the knowledge, skills and relationships to lead change for sustainable societies.</t>
         </is>
       </c>
-      <c r="E16" s="11" t="inlineStr">
+      <c r="E16" s="12" t="inlineStr">
         <is>
           <t>Evidence of innovative approaches to sustainability teaching and learning</t>
         </is>
       </c>
-      <c r="F16" s="12" t="inlineStr">
-        <is>
-          <t>In end-2025 reporting your area reported on the related SP2030 target 4a(ii) (click the ref in Column H to see it in full in Tab 3). Please build on this rather than repeating it, focusing on what is new in 2026.
-Please describe any innovative approaches used within your Faculty/Portfolio to embed sustainability in teaching and learning. This could include examples of subjects, curriculum design, pedagogies, assessment approaches or learning resources. Please provide links or supporting evidence where available.</t>
-        </is>
-      </c>
-      <c r="G16" s="12" t="inlineStr">
+      <c r="F16" s="13" t="inlineStr">
+        <is>
+          <t>Please describe any innovative approaches used within your Faculty/Portfolio to embed sustainability in teaching and learning. This could include examples of subjects, curriculum design, pedagogies, assessment approaches or learning resources. Please provide links or supporting evidence where available.
+In end-2025 reporting your area reported on the related SP2030 target 4a(ii) (click the ref in Column H to see it in full in Tab 3).</t>
+        </is>
+      </c>
+      <c r="G16" s="13" t="inlineStr">
         <is>
           <t>We will collate examples of sustainability teaching and learning, including experiential and co-curricular learning, across faculties to inform the Exceptional education section of the 2026 Sustainability Report. Strong examples may be followed up for the report.</t>
         </is>
       </c>
-      <c r="H16" s="13" t="inlineStr">
+      <c r="H16" s="14" t="inlineStr">
         <is>
           <t>4a(ii)
 → view SR25 response</t>
         </is>
       </c>
-      <c r="I16" s="12" t="inlineStr">
+      <c r="I16" s="13" t="inlineStr">
         <is>
           <t>Not yet started</t>
         </is>
       </c>
-      <c r="J16" s="12" t="inlineStr">
+      <c r="J16" s="13" t="inlineStr">
         <is>
           <t>The Joining Melbourne Module on sustainability is available to all commencing undergraduate students, and several Discovery subjects (completed by all commencing undergraduate students) embed sustainability themes. Work on embedded sustainability within the curriculum is underway at the faculty-level despite the unfunded nature of the sustainability touchstone work planned within ASE.</t>
         </is>
       </c>
-      <c r="K16" s="12" t="inlineStr">
+      <c r="K16" s="13" t="inlineStr">
         <is>
           <t>As per mid-2025: this is unfunded (including new curriculum management system). Faculties are pursuing this but central efforts are on hold.</t>
         </is>
       </c>
-      <c r="L16" s="14" t="n"/>
-      <c r="M16" s="14" t="n"/>
-      <c r="N16" s="14" t="n"/>
-      <c r="O16" s="14" t="n"/>
-      <c r="P16" s="14" t="n"/>
-      <c r="Q16" s="14" t="n"/>
+      <c r="L16" s="15" t="n"/>
+      <c r="M16" s="15" t="n"/>
+      <c r="N16" s="15" t="n"/>
+      <c r="O16" s="15" t="n"/>
+      <c r="P16" s="15" t="n"/>
+      <c r="Q16" s="15" t="n"/>
     </row>
     <row r="17" ht="150" customHeight="1">
-      <c r="B17" s="10" t="inlineStr">
+      <c r="B17" s="11" t="inlineStr">
         <is>
           <t>EE1(b)</t>
         </is>
       </c>
-      <c r="C17" s="11" t="inlineStr">
+      <c r="C17" s="12" t="inlineStr">
         <is>
           <t>Exceptional education</t>
         </is>
       </c>
-      <c r="D17" s="11" t="inlineStr">
+      <c r="D17" s="12" t="inlineStr">
         <is>
           <t>Provide our students with learning experiences that help them build the knowledge, skills and relationships to lead change for sustainable societies.</t>
         </is>
       </c>
-      <c r="E17" s="11" t="inlineStr">
+      <c r="E17" s="12" t="inlineStr">
         <is>
           <t>Pilots of possible approaches for understanding and developing students’ sustainability self-efficacy</t>
         </is>
       </c>
-      <c r="F17" s="12" t="inlineStr">
+      <c r="F17" s="13" t="inlineStr">
         <is>
           <t>Please describe any pilots or trials undertaken within your Faculty/Portfolio to understand or strengthen students’ sustainability self-efficacy. This could include the approach used, participating cohorts, what was assessed or learned, and any planned next steps.</t>
         </is>
       </c>
-      <c r="G17" s="12" t="inlineStr">
+      <c r="G17" s="13" t="inlineStr">
         <is>
           <t>This is a new indicator. We will use responses to establish a baseline of how (and whether) faculties are understanding student sustainability self-efficacy, and report on early pilots in the 2026 Sustainability Report. A nil response is useful to us.</t>
         </is>
       </c>
-      <c r="H17" s="12" t="inlineStr">
+      <c r="H17" s="13" t="inlineStr">
         <is>
           <t>N/A – new indicator</t>
         </is>
       </c>
-      <c r="I17" s="12" t="inlineStr"/>
-      <c r="J17" s="12" t="inlineStr"/>
-      <c r="K17" s="12" t="inlineStr"/>
-      <c r="L17" s="14" t="n"/>
-      <c r="M17" s="14" t="n"/>
-      <c r="N17" s="14" t="n"/>
-      <c r="O17" s="14" t="n"/>
-      <c r="P17" s="14" t="n"/>
-      <c r="Q17" s="14" t="n"/>
+      <c r="I17" s="13" t="inlineStr"/>
+      <c r="J17" s="13" t="inlineStr"/>
+      <c r="K17" s="13" t="inlineStr"/>
+      <c r="L17" s="15" t="n"/>
+      <c r="M17" s="15" t="n"/>
+      <c r="N17" s="15" t="n"/>
+      <c r="O17" s="15" t="n"/>
+      <c r="P17" s="15" t="n"/>
+      <c r="Q17" s="15" t="n"/>
     </row>
     <row r="18" ht="171" customHeight="1">
-      <c r="B18" s="10" t="inlineStr">
+      <c r="B18" s="11" t="inlineStr">
         <is>
           <t>EN1(c)</t>
         </is>
       </c>
-      <c r="C18" s="11" t="inlineStr">
+      <c r="C18" s="12" t="inlineStr">
         <is>
           <t>Enablers</t>
         </is>
       </c>
-      <c r="D18" s="11" t="inlineStr">
+      <c r="D18" s="12" t="inlineStr">
         <is>
           <t>Enablers</t>
         </is>
       </c>
-      <c r="E18" s="11" t="inlineStr">
+      <c r="E18" s="12" t="inlineStr">
         <is>
           <t>Coordinated internal engagement and external partnerships contributing to delivery of sustainability outcomes across priority areas.</t>
         </is>
       </c>
-      <c r="F18" s="12" t="inlineStr">
-        <is>
-          <t>We did not receive an end-2025 response for the related SP2030 target 3a(ii), so please include any relevant activity from across 2026.
-Please provide examples of internal engagement or external partnerships involving your Faculty/Portfolio that contributed to Sustainability 2030 outcomes, could include the priority area addressed, participating groups/partners, nature of the collaboration and key outcomes.</t>
-        </is>
-      </c>
-      <c r="G18" s="12" t="inlineStr">
+      <c r="F18" s="13" t="inlineStr">
+        <is>
+          <t>Please provide examples of internal engagement or external partnerships involving your Faculty/Portfolio that contributed to Sustainability 2030 outcomes, could include the priority area addressed, participating groups/partners, nature of the collaboration and key outcomes.
+We did not receive an end-2025 response for the related SP2030 target 3a(ii), so please include any relevant activity from across 2026.</t>
+        </is>
+      </c>
+      <c r="G18" s="13" t="inlineStr">
         <is>
           <t>We will report on internal engagement and partnerships contributing to Sustainability 2030 outcomes, and update our record of sustainability-focused communities of practice and contacts across the University.</t>
         </is>
       </c>
-      <c r="H18" s="13" t="inlineStr">
+      <c r="H18" s="14" t="inlineStr">
         <is>
           <t>3a(ii)
 → view SR25 response</t>
         </is>
       </c>
-      <c r="I18" s="12" t="inlineStr"/>
-      <c r="J18" s="12" t="inlineStr"/>
-      <c r="K18" s="12" t="inlineStr">
+      <c r="I18" s="13" t="inlineStr"/>
+      <c r="J18" s="13" t="inlineStr"/>
+      <c r="K18" s="13" t="inlineStr">
         <is>
           <t>As per mid-2025: this is not relevant to Ed portfolio. Suggest removing.</t>
         </is>
       </c>
-      <c r="L18" s="14" t="n"/>
-      <c r="M18" s="14" t="n"/>
-      <c r="N18" s="14" t="n"/>
-      <c r="O18" s="14" t="n"/>
-      <c r="P18" s="14" t="n"/>
-      <c r="Q18" s="14" t="n"/>
+      <c r="L18" s="15" t="n"/>
+      <c r="M18" s="15" t="n"/>
+      <c r="N18" s="15" t="n"/>
+      <c r="O18" s="15" t="n"/>
+      <c r="P18" s="15" t="n"/>
+      <c r="Q18" s="15" t="n"/>
     </row>
     <row r="19"/>
   </sheetData>
@@ -969,6 +1104,7 @@
     <hyperlink ref="H18" location="'3. SR25 responses'!B8"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -978,7 +1114,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F12"/>
+  <dimension ref="A1:R12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -991,104 +1127,148 @@
     <col width="22" customWidth="1" min="8" max="8"/>
     <col width="22" customWidth="1" min="9" max="9"/>
     <col width="30" customWidth="1" min="10" max="10"/>
+    <col width="13" customWidth="1" min="11" max="11"/>
+    <col width="13" customWidth="1" min="12" max="12"/>
+    <col width="13" customWidth="1" min="13" max="13"/>
+    <col width="13" customWidth="1" min="14" max="14"/>
+    <col width="13" customWidth="1" min="15" max="15"/>
+    <col width="13" customWidth="1" min="16" max="16"/>
+    <col width="13" customWidth="1" min="17" max="17"/>
+    <col width="13" customWidth="1" min="18" max="18"/>
   </cols>
   <sheetData>
-    <row r="1"/>
-    <row r="2" ht="39" customHeight="1">
-      <c r="B2" s="1" t="inlineStr">
+    <row r="1" ht="8" customHeight="1">
+      <c r="A1" s="1" t="n"/>
+      <c r="B1" s="1" t="n"/>
+      <c r="C1" s="1" t="n"/>
+      <c r="D1" s="1" t="n"/>
+      <c r="E1" s="1" t="n"/>
+      <c r="F1" s="1" t="n"/>
+      <c r="G1" s="1" t="n"/>
+      <c r="H1" s="1" t="n"/>
+      <c r="I1" s="1" t="n"/>
+      <c r="J1" s="1" t="n"/>
+      <c r="K1" s="1" t="n"/>
+      <c r="L1" s="1" t="n"/>
+      <c r="M1" s="1" t="n"/>
+      <c r="N1" s="1" t="n"/>
+      <c r="O1" s="1" t="n"/>
+      <c r="P1" s="1" t="n"/>
+      <c r="Q1" s="1" t="n"/>
+      <c r="R1" s="1" t="n"/>
+    </row>
+    <row r="2" ht="58" customHeight="1">
+      <c r="A2" s="1" t="n"/>
+      <c r="B2" s="2" t="inlineStr">
         <is>
           <t>Highlighted stories (optional)</t>
         </is>
       </c>
+      <c r="C2" s="1" t="n"/>
+      <c r="D2" s="1" t="n"/>
+      <c r="E2" s="1" t="n"/>
+      <c r="F2" s="1" t="n"/>
+      <c r="G2" s="1" t="n"/>
+      <c r="H2" s="1" t="n"/>
+      <c r="I2" s="1" t="n"/>
+      <c r="J2" s="1" t="n"/>
+      <c r="K2" s="1" t="n"/>
+      <c r="L2" s="1" t="n"/>
+      <c r="M2" s="1" t="n"/>
+      <c r="N2" s="1" t="n"/>
+      <c r="O2" s="1" t="n"/>
+      <c r="P2" s="1" t="n"/>
+      <c r="Q2" s="1" t="n"/>
+      <c r="R2" s="1" t="n"/>
     </row>
     <row r="3"/>
     <row r="4"/>
     <row r="5" ht="22" customHeight="1">
-      <c r="B5" s="15" t="inlineStr">
+      <c r="B5" s="16" t="inlineStr">
         <is>
           <t>How to use this spreadsheet</t>
         </is>
       </c>
-      <c r="C5" s="16" t="inlineStr">
-        <is>
-          <t>Please share up to 3 stories from 2026 which highlight your faculty's/portfolio's sustainability progress and/or impact. These stories can directly relate to Sustainability 2030 targets and indicators, or sustainability more generally. Due: Tuesday 15 December 2026 (early submission helps us develop case studies).</t>
+      <c r="C5" s="17" t="inlineStr">
+        <is>
+          <t>Please share up to 3 stories from 2026 which highlight your faculty's/portfolio's sustainability progress and/or impact. These stories can directly relate to Sustainability 2030 targets and indicators, or sustainability more generally. Due: Thursday 24 December 2026 (Christmas shutdown) (early submission helps us develop case studies).</t>
         </is>
       </c>
     </row>
     <row r="6"/>
     <row r="7"/>
     <row r="8" ht="39" customHeight="1">
-      <c r="B8" s="17" t="inlineStr">
+      <c r="B8" s="18" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="C8" s="17" t="inlineStr">
+      <c r="C8" s="18" t="inlineStr">
         <is>
           <t>Description</t>
         </is>
       </c>
-      <c r="D8" s="17" t="inlineStr">
+      <c r="D8" s="18" t="inlineStr">
         <is>
           <t>Related Sustainability 2030 targets (optional)</t>
         </is>
       </c>
-      <c r="E8" s="17" t="inlineStr">
+      <c r="E8" s="18" t="inlineStr">
         <is>
           <t>Images and other media</t>
         </is>
       </c>
-      <c r="F8" s="17" t="inlineStr">
+      <c r="F8" s="18" t="inlineStr">
         <is>
           <t>Links and supporting documentation</t>
         </is>
       </c>
     </row>
     <row r="9" ht="90" customHeight="1">
-      <c r="B9" s="18" t="inlineStr"/>
-      <c r="C9" s="18" t="inlineStr">
+      <c r="B9" s="19" t="inlineStr"/>
+      <c r="C9" s="19" t="inlineStr">
         <is>
           <t>• Please include a brief description of a project or activity that has made a significant contribution to sustainability at the University (up to 250 words)
 • Summarise the benefits. Benefits may relate to operational outcomes, environmental/social outcomes, and sector benefits.</t>
         </is>
       </c>
-      <c r="D9" s="18" t="inlineStr"/>
-      <c r="E9" s="18" t="inlineStr">
+      <c r="D9" s="19" t="inlineStr"/>
+      <c r="E9" s="19" t="inlineStr">
         <is>
           <t>(link to OneDrive/SharePoint files or published online content preferred)</t>
         </is>
       </c>
-      <c r="F9" s="18" t="inlineStr"/>
+      <c r="F9" s="19" t="inlineStr"/>
     </row>
     <row r="10" ht="120" customHeight="1">
       <c r="A10" t="n">
         <v>1</v>
       </c>
-      <c r="B10" s="14" t="n"/>
-      <c r="C10" s="14" t="n"/>
-      <c r="D10" s="14" t="n"/>
-      <c r="E10" s="14" t="n"/>
-      <c r="F10" s="14" t="n"/>
+      <c r="B10" s="15" t="n"/>
+      <c r="C10" s="15" t="n"/>
+      <c r="D10" s="15" t="n"/>
+      <c r="E10" s="15" t="n"/>
+      <c r="F10" s="15" t="n"/>
     </row>
     <row r="11" ht="120" customHeight="1">
       <c r="A11" t="n">
         <v>2</v>
       </c>
-      <c r="B11" s="14" t="n"/>
-      <c r="C11" s="14" t="n"/>
-      <c r="D11" s="14" t="n"/>
-      <c r="E11" s="14" t="n"/>
-      <c r="F11" s="14" t="n"/>
+      <c r="B11" s="15" t="n"/>
+      <c r="C11" s="15" t="n"/>
+      <c r="D11" s="15" t="n"/>
+      <c r="E11" s="15" t="n"/>
+      <c r="F11" s="15" t="n"/>
     </row>
     <row r="12" ht="120" customHeight="1">
       <c r="A12" t="n">
         <v>3</v>
       </c>
-      <c r="B12" s="14" t="n"/>
-      <c r="C12" s="14" t="n"/>
-      <c r="D12" s="14" t="n"/>
-      <c r="E12" s="14" t="n"/>
-      <c r="F12" s="14" t="n"/>
+      <c r="B12" s="15" t="n"/>
+      <c r="C12" s="15" t="n"/>
+      <c r="D12" s="15" t="n"/>
+      <c r="E12" s="15" t="n"/>
+      <c r="F12" s="15" t="n"/>
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="1"/>
@@ -1096,6 +1276,7 @@
     <mergeCell ref="C5:F6"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -1105,7 +1286,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I11"/>
+  <dimension ref="A1:R11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -1117,244 +1298,289 @@
     <col width="60" customWidth="1" min="7" max="7"/>
     <col width="34" customWidth="1" min="8" max="8"/>
     <col width="16" customWidth="1" min="9" max="9"/>
+    <col width="13" customWidth="1" min="10" max="10"/>
+    <col width="13" customWidth="1" min="11" max="11"/>
+    <col width="13" customWidth="1" min="12" max="12"/>
+    <col width="13" customWidth="1" min="13" max="13"/>
+    <col width="13" customWidth="1" min="14" max="14"/>
+    <col width="13" customWidth="1" min="15" max="15"/>
+    <col width="13" customWidth="1" min="16" max="16"/>
+    <col width="13" customWidth="1" min="17" max="17"/>
+    <col width="13" customWidth="1" min="18" max="18"/>
   </cols>
   <sheetData>
-    <row r="1"/>
-    <row r="2" ht="39" customHeight="1">
-      <c r="B2" s="1" t="inlineStr">
+    <row r="1" ht="8" customHeight="1">
+      <c r="A1" s="1" t="n"/>
+      <c r="B1" s="1" t="n"/>
+      <c r="C1" s="1" t="n"/>
+      <c r="D1" s="1" t="n"/>
+      <c r="E1" s="1" t="n"/>
+      <c r="F1" s="1" t="n"/>
+      <c r="G1" s="1" t="n"/>
+      <c r="H1" s="1" t="n"/>
+      <c r="I1" s="1" t="n"/>
+      <c r="J1" s="1" t="n"/>
+      <c r="K1" s="1" t="n"/>
+      <c r="L1" s="1" t="n"/>
+      <c r="M1" s="1" t="n"/>
+      <c r="N1" s="1" t="n"/>
+      <c r="O1" s="1" t="n"/>
+      <c r="P1" s="1" t="n"/>
+      <c r="Q1" s="1" t="n"/>
+      <c r="R1" s="1" t="n"/>
+    </row>
+    <row r="2" ht="58" customHeight="1">
+      <c r="A2" s="1" t="n"/>
+      <c r="B2" s="2" t="inlineStr">
         <is>
           <t>Your SR25 responses – Chancellery Education</t>
         </is>
       </c>
+      <c r="C2" s="1" t="n"/>
+      <c r="D2" s="1" t="n"/>
+      <c r="E2" s="1" t="n"/>
+      <c r="F2" s="1" t="n"/>
+      <c r="G2" s="1" t="n"/>
+      <c r="H2" s="1" t="n"/>
+      <c r="I2" s="1" t="n"/>
+      <c r="J2" s="1" t="n"/>
+      <c r="K2" s="1" t="n"/>
+      <c r="L2" s="1" t="n"/>
+      <c r="M2" s="1" t="n"/>
+      <c r="N2" s="1" t="n"/>
+      <c r="O2" s="1" t="n"/>
+      <c r="P2" s="1" t="n"/>
+      <c r="Q2" s="1" t="n"/>
+      <c r="R2" s="1" t="n"/>
     </row>
     <row r="3" ht="32" customHeight="1">
-      <c r="B3" s="16" t="inlineStr">
+      <c r="B3" s="17" t="inlineStr">
         <is>
           <t>Your responses to the end-2025 reporting request, against the former Sustainability Plan 2030 (SP2030) targets. For reference only – please do not edit. Use the 'Back to request' links to return to the reporting template.</t>
         </is>
       </c>
     </row>
     <row r="4" ht="22" customHeight="1">
-      <c r="B4" s="19" t="inlineStr">
+      <c r="B4" s="20" t="inlineStr">
         <is>
           <t>← Back to request</t>
         </is>
       </c>
     </row>
     <row r="5" ht="30" customHeight="1">
-      <c r="B5" s="20" t="inlineStr">
+      <c r="B5" s="21" t="inlineStr">
         <is>
           <t>Chancellery Education</t>
         </is>
       </c>
     </row>
     <row r="6" ht="42" customHeight="1">
-      <c r="B6" s="7" t="inlineStr">
+      <c r="B6" s="8" t="inlineStr">
         <is>
           <t>SR25 ref</t>
         </is>
       </c>
-      <c r="C6" s="7" t="inlineStr">
+      <c r="C6" s="8" t="inlineStr">
         <is>
           <t>SP2030 target</t>
         </is>
       </c>
-      <c r="D6" s="7" t="inlineStr">
+      <c r="D6" s="8" t="inlineStr">
         <is>
           <t>2025 reporting request</t>
         </is>
       </c>
-      <c r="E6" s="7" t="inlineStr">
+      <c r="E6" s="8" t="inlineStr">
         <is>
           <t>Confirmed end-2025 status</t>
         </is>
       </c>
-      <c r="F6" s="7" t="inlineStr">
+      <c r="F6" s="8" t="inlineStr">
         <is>
           <t>OPTION 1: Target-level reporting</t>
         </is>
       </c>
-      <c r="G6" s="7" t="inlineStr">
+      <c r="G6" s="8" t="inlineStr">
         <is>
           <t>OPTION 2: Indicator-level reporting</t>
         </is>
       </c>
-      <c r="H6" s="7" t="inlineStr">
+      <c r="H6" s="8" t="inlineStr">
         <is>
           <t>Supporting information/comments</t>
         </is>
       </c>
-      <c r="I6" s="7" t="inlineStr">
+      <c r="I6" s="8" t="inlineStr">
         <is>
           <t>Related SR26 indicator(s)</t>
         </is>
       </c>
     </row>
     <row r="7" ht="160" customHeight="1">
-      <c r="B7" s="10" t="inlineStr">
+      <c r="B7" s="11" t="inlineStr">
         <is>
           <t>3a(i)</t>
         </is>
       </c>
-      <c r="C7" s="12" t="inlineStr">
+      <c r="C7" s="13" t="inlineStr">
         <is>
           <t>The University's Academic Divisions and portfolios support and learn from each other to embed sustainability in practice and in learning – formal, non-formal and informal</t>
         </is>
       </c>
-      <c r="D7" s="12" t="inlineStr">
+      <c r="D7" s="13" t="inlineStr">
         <is>
           <t>List and describe the role of staff focused on sustainability touchstone in Chancellery Education.</t>
         </is>
       </c>
-      <c r="E7" s="12" t="inlineStr">
+      <c r="E7" s="13" t="inlineStr">
         <is>
           <t>Not provided</t>
         </is>
       </c>
-      <c r="F7" s="12" t="inlineStr"/>
-      <c r="G7" s="12" t="inlineStr"/>
-      <c r="H7" s="12" t="inlineStr">
+      <c r="F7" s="13" t="inlineStr"/>
+      <c r="G7" s="13" t="inlineStr"/>
+      <c r="H7" s="13" t="inlineStr">
         <is>
           <t>As per mid-2025: this is not relevant to Ed portfolio. Suggest removing.</t>
         </is>
       </c>
-      <c r="I7" s="12" t="inlineStr"/>
+      <c r="I7" s="13" t="inlineStr"/>
     </row>
     <row r="8" ht="160" customHeight="1">
-      <c r="B8" s="10" t="inlineStr">
+      <c r="B8" s="11" t="inlineStr">
         <is>
           <t>3a(ii)</t>
         </is>
       </c>
-      <c r="C8" s="12" t="inlineStr">
+      <c r="C8" s="13" t="inlineStr">
         <is>
           <t>The University's Academic Divisions and portfolios support and learn from each other to embed sustainability in practice and in learning – formal, non-formal and informal</t>
         </is>
       </c>
-      <c r="D8" s="12" t="inlineStr">
+      <c r="D8" s="13" t="inlineStr">
         <is>
           <t>List and describe any sustainability-focused communities of practice in the Portfolio; their purpose, activities and outcomes.</t>
         </is>
       </c>
-      <c r="E8" s="12" t="inlineStr">
+      <c r="E8" s="13" t="inlineStr">
         <is>
           <t>Not provided</t>
         </is>
       </c>
-      <c r="F8" s="12" t="inlineStr"/>
-      <c r="G8" s="12" t="inlineStr"/>
-      <c r="H8" s="12" t="inlineStr">
+      <c r="F8" s="13" t="inlineStr"/>
+      <c r="G8" s="13" t="inlineStr"/>
+      <c r="H8" s="13" t="inlineStr">
         <is>
           <t>As per mid-2025: this is not relevant to Ed portfolio. Suggest removing.</t>
         </is>
       </c>
-      <c r="I8" s="12" t="inlineStr">
+      <c r="I8" s="13" t="inlineStr">
         <is>
           <t>EN1(c)</t>
         </is>
       </c>
     </row>
     <row r="9" ht="160" customHeight="1">
-      <c r="B9" s="10" t="inlineStr">
+      <c r="B9" s="11" t="inlineStr">
         <is>
           <t>3d(ii)</t>
         </is>
       </c>
-      <c r="C9" s="12" t="inlineStr">
+      <c r="C9" s="13" t="inlineStr">
         <is>
           <t>Academic and professional staff have increased their participation in and contribution to formal and non_x0002_formal learning to develop their general and role-specific sustainability skills</t>
         </is>
       </c>
-      <c r="D9" s="12" t="inlineStr">
+      <c r="D9" s="13" t="inlineStr">
         <is>
           <t>Number of professional staff who have undertaken professional development related to Education for Sustainability</t>
         </is>
       </c>
-      <c r="E9" s="12" t="inlineStr">
+      <c r="E9" s="13" t="inlineStr">
         <is>
           <t>Not provided</t>
         </is>
       </c>
-      <c r="F9" s="12" t="inlineStr"/>
-      <c r="G9" s="12" t="inlineStr"/>
-      <c r="H9" s="12" t="inlineStr">
+      <c r="F9" s="13" t="inlineStr"/>
+      <c r="G9" s="13" t="inlineStr"/>
+      <c r="H9" s="13" t="inlineStr">
         <is>
           <t>As per mid-2025: this is not relevant to Ed portfolio. Suggest removing.</t>
         </is>
       </c>
-      <c r="I9" s="12" t="inlineStr"/>
+      <c r="I9" s="13" t="inlineStr"/>
     </row>
     <row r="10" ht="160" customHeight="1">
-      <c r="B10" s="10" t="inlineStr">
+      <c r="B10" s="11" t="inlineStr">
         <is>
           <t>4a(ii)</t>
         </is>
       </c>
-      <c r="C10" s="12" t="inlineStr">
+      <c r="C10" s="13" t="inlineStr">
         <is>
           <t>Sustainability is integrated into curriculum to an extent that conscientiously extends, beyond a base threshold, each discipline’s (and associated professions/industries’) knowledge of the helpful and harmful impacts it has for the environmental and human systems we depend on</t>
         </is>
       </c>
-      <c r="D10" s="12" t="inlineStr">
+      <c r="D10" s="13" t="inlineStr">
         <is>
           <t>Describe work in Chancellery Education in 2025 related to the sustainability touchstone in the Advancing Students and Education strategy</t>
         </is>
       </c>
-      <c r="E10" s="12" t="inlineStr">
+      <c r="E10" s="13" t="inlineStr">
         <is>
           <t>Not yet started</t>
         </is>
       </c>
-      <c r="F10" s="12" t="inlineStr">
+      <c r="F10" s="13" t="inlineStr">
         <is>
           <t>The Joining Melbourne Module on sustainability is available to all commencing undergraduate students, and several Discovery subjects (completed by all commencing undergraduate students) embed sustainability themes. Work on embedded sustainability within the curriculum is underway at the faculty-level despite the unfunded nature of the sustainability touchstone work planned within ASE.</t>
         </is>
       </c>
-      <c r="G10" s="12" t="inlineStr"/>
-      <c r="H10" s="12" t="inlineStr">
+      <c r="G10" s="13" t="inlineStr"/>
+      <c r="H10" s="13" t="inlineStr">
         <is>
           <t>As per mid-2025: this is unfunded (including new curriculum management system). Faculties are pursuing this but central efforts are on hold.</t>
         </is>
       </c>
-      <c r="I10" s="12" t="inlineStr">
+      <c r="I10" s="13" t="inlineStr">
         <is>
           <t>EE1(a)</t>
         </is>
       </c>
     </row>
     <row r="11" ht="160" customHeight="1">
-      <c r="B11" s="10" t="inlineStr">
+      <c r="B11" s="11" t="inlineStr">
         <is>
           <t>4b(i)</t>
         </is>
       </c>
-      <c r="C11" s="12" t="inlineStr">
+      <c r="C11" s="13" t="inlineStr">
         <is>
           <t>Graduates have increased capabilities to shape, lead and succeed in the careers, communities and industries of sustainable societies (year on year).</t>
         </is>
       </c>
-      <c r="D11" s="12" t="inlineStr">
+      <c r="D11" s="13" t="inlineStr">
         <is>
           <t>Is there any way to measure graduate outcomes related to sustainability in Chancellery Education? If so, please describe.</t>
         </is>
       </c>
-      <c r="E11" s="12" t="inlineStr">
+      <c r="E11" s="13" t="inlineStr">
         <is>
           <t>Not yet started</t>
         </is>
       </c>
-      <c r="F11" s="12" t="inlineStr">
+      <c r="F11" s="13" t="inlineStr">
         <is>
           <t>Facukty work in this area has continued across the University, as has work in co-curricular programs such as Melbourne Plus (see SASS respose, below). These continue to build and enhance graduate capabilities.</t>
         </is>
       </c>
-      <c r="G11" s="12" t="inlineStr"/>
-      <c r="H11" s="12" t="inlineStr">
+      <c r="G11" s="13" t="inlineStr"/>
+      <c r="H11" s="13" t="inlineStr">
         <is>
           <t>As per mid-2025: this is unfunded (including new curriculum management system). Faculties are pursuing this but central efforts are on hold.</t>
         </is>
       </c>
-      <c r="I11" s="12" t="inlineStr"/>
+      <c r="I11" s="13" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -1364,6 +1590,7 @@
     <hyperlink ref="B4" location="'1. Reporting template'!A1"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
 

--- a/output/central_unit_requests/Education - SR26 sustainability reporting request.xlsx
+++ b/output/central_unit_requests/Education - SR26 sustainability reporting request.xlsx
@@ -703,9 +703,9 @@
     <col width="48" customWidth="1" min="12" max="12"/>
     <col width="48" customWidth="1" min="13" max="13"/>
     <col width="30" customWidth="1" min="14" max="14"/>
-    <col width="30" customWidth="1" min="15" max="15"/>
-    <col width="20" customWidth="1" min="16" max="16"/>
-    <col width="24" customWidth="1" min="17" max="17"/>
+    <col width="36" customWidth="1" min="15" max="15"/>
+    <col width="13" customWidth="1" min="16" max="16"/>
+    <col width="13" customWidth="1" min="17" max="17"/>
     <col width="13" customWidth="1" min="18" max="18"/>
   </cols>
   <sheetData>
@@ -764,7 +764,8 @@
         <is>
           <t>• For each row below, describe progress towards the target (Column L) and/or respond to the 2026 reporting request (Column M)
 • Provide supporting information if required (Column N), including links to documents or images
-• Note the source of your information and any limitations (Column O), then confirm the information is accurate (Columns P–Q)
+• Note the source of your information, any limitations and the person closest to the data (Column O)
+• Please return the spreadsheet once it has been reviewed and confirmed by your area's senior lead
 • Where a related end-2025 target existed, click the ref in Column H to see your full SR25 response (Tab 3)
 • Use Tab 2 of this spreadsheet to highlight key sustainability stories (optional)
 • 2026 is a transition year: Sustainability 2030 launched ~20 October 2026, so report on activity across all of 2026 and any early actions since launch. No target status rating is requested this year.
@@ -803,7 +804,7 @@
         </is>
       </c>
     </row>
-    <row r="14" ht="60" customHeight="1">
+    <row r="14" ht="42" customHeight="1">
       <c r="B14" s="8" t="inlineStr">
         <is>
           <t>Ref</t>
@@ -871,17 +872,7 @@
       </c>
       <c r="O14" s="9" t="inlineStr">
         <is>
-          <t>Data source and limitations</t>
-        </is>
-      </c>
-      <c r="P14" s="9" t="inlineStr">
-        <is>
-          <t>Data owner confirms information is accurate</t>
-        </is>
-      </c>
-      <c r="Q14" s="9" t="inlineStr">
-        <is>
-          <t>Confirmed by (name, role, date)</t>
+          <t>Data source, limitations and contact person</t>
         </is>
       </c>
     </row>
@@ -913,17 +904,7 @@
       </c>
       <c r="O15" s="10" t="inlineStr">
         <is>
-          <t>Where did this information come from (system, report, survey, person)? Note any gaps or limitations.</t>
-        </is>
-      </c>
-      <c r="P15" s="10" t="inlineStr">
-        <is>
-          <t>Select 'Yes' to confirm the information provided is accurate and can be used for reporting</t>
-        </is>
-      </c>
-      <c r="Q15" s="10" t="inlineStr">
-        <is>
-          <t>Name, role and date of the person confirming</t>
+          <t>Where did this information come from (system, report, survey)? Note any gaps or limitations, and the person closest to the data we can follow up with.</t>
         </is>
       </c>
     </row>
@@ -950,7 +931,7 @@
       </c>
       <c r="F16" s="13" t="inlineStr">
         <is>
-          <t>Please describe any innovative approaches used within your Faculty/Portfolio to embed sustainability in teaching and learning. This could include examples of subjects, curriculum design, pedagogies, assessment approaches or learning resources. Please provide links or supporting evidence where available.
+          <t>Please describe any innovative approaches used within your portfolio to embed sustainability in teaching and learning. This could include examples of subjects, curriculum design, pedagogies, assessment approaches or learning resources. Please provide links or supporting evidence where available.
 In end-2025 reporting your area reported on the related SP2030 target 4a(ii) (click the ref in Column H to see it in full in Tab 3).</t>
         </is>
       </c>
@@ -984,8 +965,6 @@
       <c r="M16" s="15" t="n"/>
       <c r="N16" s="15" t="n"/>
       <c r="O16" s="15" t="n"/>
-      <c r="P16" s="15" t="n"/>
-      <c r="Q16" s="15" t="n"/>
     </row>
     <row r="17" ht="150" customHeight="1">
       <c r="B17" s="11" t="inlineStr">
@@ -1010,7 +989,7 @@
       </c>
       <c r="F17" s="13" t="inlineStr">
         <is>
-          <t>Please describe any pilots or trials undertaken within your Faculty/Portfolio to understand or strengthen students’ sustainability self-efficacy. This could include the approach used, participating cohorts, what was assessed or learned, and any planned next steps.</t>
+          <t>Please describe any pilots or trials undertaken within your portfolio to understand or strengthen students’ sustainability self-efficacy. This could include the approach used, participating cohorts, what was assessed or learned, and any planned next steps.</t>
         </is>
       </c>
       <c r="G17" s="13" t="inlineStr">
@@ -1030,10 +1009,8 @@
       <c r="M17" s="15" t="n"/>
       <c r="N17" s="15" t="n"/>
       <c r="O17" s="15" t="n"/>
-      <c r="P17" s="15" t="n"/>
-      <c r="Q17" s="15" t="n"/>
-    </row>
-    <row r="18" ht="171" customHeight="1">
+    </row>
+    <row r="18" ht="154" customHeight="1">
       <c r="B18" s="11" t="inlineStr">
         <is>
           <t>EN1(c)</t>
@@ -1056,13 +1033,13 @@
       </c>
       <c r="F18" s="13" t="inlineStr">
         <is>
-          <t>Please provide examples of internal engagement or external partnerships involving your Faculty/Portfolio that contributed to Sustainability 2030 outcomes, could include the priority area addressed, participating groups/partners, nature of the collaboration and key outcomes.
+          <t>Please provide examples of internal engagement or external partnerships involving your portfolio that contributed to sustainability outcomes, could include the priority area addressed, participating groups/partners, nature of the collaboration and key outcomes.
 We did not receive an end-2025 response for the related SP2030 target 3a(ii), so please include any relevant activity from across 2026.</t>
         </is>
       </c>
       <c r="G18" s="13" t="inlineStr">
         <is>
-          <t>We will report on internal engagement and partnerships contributing to Sustainability 2030 outcomes, and update our record of sustainability-focused communities of practice and contacts across the University.</t>
+          <t>We will report on internal engagement and partnerships contributing to sustainability outcomes, and update our record of sustainability-focused communities of practice and contacts across the University.</t>
         </is>
       </c>
       <c r="H18" s="14" t="inlineStr">
@@ -1082,23 +1059,16 @@
       <c r="M18" s="15" t="n"/>
       <c r="N18" s="15" t="n"/>
       <c r="O18" s="15" t="n"/>
-      <c r="P18" s="15" t="n"/>
-      <c r="Q18" s="15" t="n"/>
     </row>
     <row r="19"/>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="1"/>
   <mergeCells count="4">
     <mergeCell ref="C13:G13"/>
-    <mergeCell ref="L13:Q13"/>
+    <mergeCell ref="L13:O13"/>
     <mergeCell ref="D4:G8"/>
     <mergeCell ref="B4:C8"/>
   </mergeCells>
-  <dataValidations count="1">
-    <dataValidation sqref="P16:P18" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid entry" error="Please select from the dropdown" type="list">
-      <formula1>=Lists!$C$2:$C$4</formula1>
-    </dataValidation>
-  </dataValidations>
   <hyperlinks>
     <hyperlink ref="H16" location="'3. SR25 responses'!B10"/>
     <hyperlink ref="H18" location="'3. SR25 responses'!B8"/>
